--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet_1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet_2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,139 +425,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Parameter</t>
+          <t>Function No</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Function Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Usage Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>int, float</t>
+          <t>num(a, b)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The first operand for the addition operation.</t>
+          <t>The `num` function calculates and returns the sum of two provided numbers.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Description | The first number to add. | The second number to add. |</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>This function provides a straightforward way to perform addition. It accepts two arguments, `a` and `b`, which are expected to be numerical values (integers or floating-point numbers). The core logic of the function is to use the `+` operator to compute the sum of `a` and `b`. The resulting value is then returned to the caller. For example, if `a` is `5` and `b` is `10`, the function will compute `5 + 10` and return `15`.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>- This function is designed for numeric types like `int` and `float`. - If string values are passed as arguments, the function will perform string concatenation instead of mathematical addition (e.g., `num("hello", "world")` would return `"helloworld"`). - The type of the returned value will depend on the types of the input parameters (e.g., adding two integers returns an integer; adding an integer and a float returns a float). **Output Example**: A numeric value representing the sum. `15`</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>int, float</t>
+          <t>generate_random_integers(count, start, end)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The second operand for the addition operation.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>The total number of integers to generate in the list.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>The inclusive lower bound for the random values. Defaults to 0.</t>
+          <t>The `generate_random_integers` function generates a list of a specified number of pseudo-random integers within a given inclusive range.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Description | The number of random integers to generate. This value must be non-negative. | The inclusive lower bound for the random numbers. Defaults to `0`. | The inclusive upper bound for the random numbers. Defaults to `100`. |</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>This function provides a convenient way to create a list of pseudo-random integers. Its operation can be broken down into three main steps: 1. **Input Validation**: The function first checks if the `count` parameter is a non-negative number. If `count` is less than zero, it is considered invalid for generating a list, and the function will raise a `ValueError`. 2. **Boundary Correction**: It then compares the `start` and `end` parameters. If `start` is found to be greater than `end`, the func...</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>- This function requires the `random` module to be imported in the script. - If the `start` value is greater than the `end` value, they will be swapped internally to ensure a valid range. - Providing a negative value for the `count` parameter will raise a `ValueError`. - The default behavior, if no `start` or `end` is provided, is to generate numbers in the range `[0, 100]`. **Output Example**: The function returns a list of integers. The length of the list will be equal to the `count` parame...</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>fibonacci(n)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The inclusive upper bound for the random values. Defaults to 100.</t>
+          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an iterative approach.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the number.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>This function provides a memory-efficient, iterative method to calculate a Fibonacci number. The logic proceeds as follows: 1. **Input Validation**: The function first checks if the input `n` is a negative number. Since the Fibonacci sequence is not defined for negative indices, it raises a `ValueError` if this condition is met. 2. **Initialization**: Two variables, `a` and `b`, are initialized to `0` and `1` respectively. These represent the first two numbers in the sequence, F₀ and F₁. 3. *...</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>- The input `n` must be a non-negative integer. The function will raise a `ValueError` for negative inputs. - The sequence is 0-indexed, meaning `fibonacci(0)` returns the first number in the sequence, which is `0`. - This iterative implementation is efficient in terms of memory and performance for large values of `n` compared to a naive recursive approach, as it avoids deep recursion stacks. **Output Example**: The function returns a single integer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>choose_random_item(items)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The `choose_random_item` function selects and returns a single random item from a given non-empty list of strings.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>- `items` (`List[str]`): A list of strings to choose from. This list must not be empty.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>This function provides a safe way to select a random element from a list of strings. The function first performs a validation check on the input `items` list. It uses the condition `if not items` to determine if the list is empty. If the list has no elements, the condition is `True`, and the function raises a `ValueError` with the message "items must not be empty". This prevents runtime errors that would occur if trying to select an item from an empty sequence. If the list is not empty, the f...</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>- The input list `items` must contain at least one element. Providing an empty list will result in a `ValueError`. - This function requires the `random` module to be imported in the execution environment. - The selection is uniformly random, meaning every item in the list has an equal probability of being chosen. **Output Example**: A single string from the input list, such as `"cherry"`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>shuffle_copy(items)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original list remains unchanged.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>- `items` (`List[int]`): A list of integers that will be copied and then shuffled.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>This function provides a safe way to shuffle a list without altering the original data structure. The process is executed in three main steps: 1. A shallow copy of the input `items` list is created using the `list()` constructor. This new list is stored in a variable named `copy`. This step is crucial for preserving the original list. 2. The `random.shuffle()` function is then called on the `copy`. `random.shuffle()` shuffles the elements of a sequence *in-place*, meaning it directly modifies...</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>- This function is non-mutating. It will not change the order of the original list passed as the `items` argument. - The function depends on Python's built-in `random` module. Ensure that `import random` is present in the file where this function is used. - The returned value is a new list object, not a reference to the original. - While the type hint specifies `List[int]`, the function will work correctly with lists containing any type of element (e.g., strings, floats, or mixed types). **Ou...</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -479,22 +479,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The `num` function calculates and returns the sum of two provided numbers.</t>
+          <t>The `num` function calculates and returns the sum of two provided arguments.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Description | The first number to add. | The second number to add. |</t>
+          <t>Description | The first number to be added. | The second number to be added. |</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to perform addition. It accepts two arguments, `a` and `b`, which are expected to be numerical values (integers or floating-point numbers). The core logic of the function is to use the `+` operator to compute the sum of `a` and `b`. The resulting value is then returned to the caller. For example, if `a` is `5` and `b` is `10`, the function will compute `5 + 10` and return `15`.</t>
+          <t>This function performs a basic addition operation. It takes two parameters, `a` and `b`, which are expected to be numeric types such as integers or floats. The function uses the standard addition operator (`+`) to compute their sum. The resulting value is then returned by the function. For example, if `a` is `5` and `b` is `10`, the function will compute `5 + 10` and return `15`.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>- This function is designed for numeric types like `int` and `float`. - If string values are passed as arguments, the function will perform string concatenation instead of mathematical addition (e.g., `num("hello", "world")` would return `"helloworld"`). - The type of the returned value will depend on the types of the input parameters (e.g., adding two integers returns an integer; adding an integer and a float returns a float). **Output Example**: A numeric value representing the sum. `15`</t>
+          <t>- This function is designed for numeric types (`int`, `float`). - If string values are passed as arguments, the function will perform string concatenation instead of mathematical addition (e.g., `num("hello", " world")` returns `"hello world"`). - Passing incompatible types (e.g., an integer and a string) will result in a `TypeError`. **Output Example**: The function returns a single value of the same or a promoted numeric type (e.g., adding an `int` and a `float` results in a `float`).</t>
         </is>
       </c>
     </row>
@@ -509,22 +509,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The `generate_random_integers` function generates a list of a specified number of pseudo-random integers within a given inclusive range.</t>
+          <t>The `generate_random_integers` function returns a list containing a specified number of pseudo-random integers within a defined inclusive range.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Description | The number of random integers to generate. This value must be non-negative. | The inclusive lower bound for the random numbers. Defaults to `0`. | The inclusive upper bound for the random numbers. Defaults to `100`. |</t>
+          <t>Description | The total number of integers to generate in the list. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>This function provides a convenient way to create a list of pseudo-random integers. Its operation can be broken down into three main steps: 1. **Input Validation**: The function first checks if the `count` parameter is a non-negative number. If `count` is less than zero, it is considered invalid for generating a list, and the function will raise a `ValueError`. 2. **Boundary Correction**: It then compares the `start` and `end` parameters. If `start` is found to be greater than `end`, the func...</t>
+          <t>This function provides a straightforward way to generate a list of random integers. The process is as follows: 1. **Input Validation**: The function first validates the `count` parameter. If `count` is a negative number, it raises a `ValueError` because it's impossible to generate a negative number of items. 2. **Range Correction**: It checks if the `start` value is greater than the `end` value. If it is, the function automatically swaps them. This ensures that `random.randint` receives a val...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>- This function requires the `random` module to be imported in the script. - If the `start` value is greater than the `end` value, they will be swapped internally to ensure a valid range. - Providing a negative value for the `count` parameter will raise a `ValueError`. - The default behavior, if no `start` or `end` is provided, is to generate numbers in the range `[0, 100]`. **Output Example**: The function returns a list of integers. The length of the list will be equal to the `count` parame...</t>
+          <t>- This function depends on Python's built-in `random` module. Ensure it is imported before use. - The `count` parameter must be a non-negative integer. - Both the `start` and `end` boundaries are inclusive, meaning they can appear in the output list. - If `start` is provided as a larger number than `end`, the function will automatically swap them and proceed without error. **Output Example**: A call to `generate_random_integers(5, 1, 10)` might produce a list like this:</t>
         </is>
       </c>
     </row>
@@ -539,22 +539,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an iterative approach.</t>
+          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an efficient iterative approach.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the number.</t>
+          <t>- `n`: `int` - The 0-indexed position in the Fibonacci sequence for which to find the corresponding number.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>This function provides a memory-efficient, iterative method to calculate a Fibonacci number. The logic proceeds as follows: 1. **Input Validation**: The function first checks if the input `n` is a negative number. Since the Fibonacci sequence is not defined for negative indices, it raises a `ValueError` if this condition is met. 2. **Initialization**: Two variables, `a` and `b`, are initialized to `0` and `1` respectively. These represent the first two numbers in the sequence, F₀ and F₁. 3. *...</t>
+          <t>This function calculates a Fibonacci number based on its index `n`. The Fibonacci sequence is a series of numbers where each number is the sum of the two preceding ones, usually starting with 0 and 1. The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError`, as the Fibonacci sequence is defined for non-negative integers. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequence (F...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>- The input `n` must be a non-negative integer. The function will raise a `ValueError` for negative inputs. - The sequence is 0-indexed, meaning `fibonacci(0)` returns the first number in the sequence, which is `0`. - This iterative implementation is efficient in terms of memory and performance for large values of `n` compared to a naive recursive approach, as it avoids deep recursion stacks. **Output Example**: The function returns a single integer.</t>
+          <t>- The input `n` must be a non-negative integer. Providing a negative integer will result in a `ValueError`. - The function uses a 0-indexed sequence. For example, `fibonacci(0)` returns `0`, `fibonacci(1)` returns `1`, and so on. - This iterative implementation is highly efficient in terms of memory and performance for large values of `n` compared to a naive recursive approach, as it avoids redundant calculations and deep recursion stacks. **Output Example**: The function returns a single int...</t>
         </is>
       </c>
     </row>
@@ -569,22 +569,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single random item from a given non-empty list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single random element from a given list of strings.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>- `items` (`List[str]`): A list of strings to choose from. This list must not be empty.</t>
+          <t>- **`items`** (`List[str]`): A list of strings from which to choose a random item. This list must not be empty.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>This function provides a safe way to select a random element from a list of strings. The function first performs a validation check on the input `items` list. It uses the condition `if not items` to determine if the list is empty. If the list has no elements, the condition is `True`, and the function raises a `ValueError` with the message "items must not be empty". This prevents runtime errors that would occur if trying to select an item from an empty sequence. If the list is not empty, the f...</t>
+          <t>This function provides a simple way to get a random item from a sequence. The core logic is implemented in two steps: 1. **Input Validation**: The function first checks if the provided `items` list is empty using the condition `if not items:`. If the list is empty, it raises a `ValueError` with the message "items must not be empty". This is a crucial safeguard to prevent the underlying `random.choice` function from failing, as it requires a non-empty sequence. 2. **Random Selection**: If the ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>- The input list `items` must contain at least one element. Providing an empty list will result in a `ValueError`. - This function requires the `random` module to be imported in the execution environment. - The selection is uniformly random, meaning every item in the list has an equal probability of being chosen. **Output Example**: A single string from the input list, such as `"cherry"`.</t>
+          <t>- The input list `items` must contain at least one element. Providing an empty list will result in a `ValueError`. - This function depends on Python's built-in `random` module. Ensure that `import random` is present at the top of your script. - Each item in the list has an equal probability of being selected. **Output Example**: A single string from the input list. For an input of `["red", "green", "blue"]`, a possible return value is `"green"`.</t>
         </is>
       </c>
     </row>
@@ -599,22 +599,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original list remains unchanged.</t>
+          <t>The `shuffle_copy` function creates and returns a randomly shuffled copy of a list of integers, leaving the original list unchanged.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>- `items` (`List[int]`): A list of integers that will be copied and then shuffled.</t>
+          <t>- `items` (`List[int]`): The list of integers to be copied and shuffled.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>This function provides a safe way to shuffle a list without altering the original data structure. The process is executed in three main steps: 1. A shallow copy of the input `items` list is created using the `list()` constructor. This new list is stored in a variable named `copy`. This step is crucial for preserving the original list. 2. The `random.shuffle()` function is then called on the `copy`. `random.shuffle()` shuffles the elements of a sequence *in-place*, meaning it directly modifies...</t>
+          <t>This function provides a non-destructive way to shuffle a list. The logic proceeds in three steps: First, it creates a shallow copy of the input `items` list by calling `list(items)`. This ensures that any subsequent modifications do not affect the original list that was passed to the function. Next, it uses the `random.shuffle()` method to shuffle the elements of the newly created `copy` list in-place. This function rearranges the items in the list into a random order. Finally, the function ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>- This function is non-mutating. It will not change the order of the original list passed as the `items` argument. - The function depends on Python's built-in `random` module. Ensure that `import random` is present in the file where this function is used. - The returned value is a new list object, not a reference to the original. - While the type hint specifies `List[int]`, the function will work correctly with lists containing any type of element (e.g., strings, floats, or mixed types). **Ou...</t>
+          <t>- The primary feature of this function is that it is non-mutating. The original list passed as the `items` parameter will remain in its original order after the function completes. - This function depends on Python's `random` module. Ensure that `import random` is present at the top of the script where this function is defined or called. - While the type hint specifies `List[int]`, the function's logic will work correctly with lists containing other data types (e.g., strings, floats, or mixed...</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,37 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E8F5"/>
+        <bgColor rgb="00D9E8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +79,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,153 +504,153 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>num(a, b)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>The `num` function calculates and returns the sum of two provided arguments.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>The `num` function calculates and returns the sum of two input arguments.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Description | The first number to be added. | The second number to be added. |</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>This function performs a basic addition operation. It takes two parameters, `a` and `b`, which are expected to be numeric types such as integers or floats. The function uses the standard addition operator (`+`) to compute their sum. The resulting value is then returned by the function. For example, if `a` is `5` and `b` is `10`, the function will compute `5 + 10` and return `15`.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>- This function is designed for numeric types (`int`, `float`). - If string values are passed as arguments, the function will perform string concatenation instead of mathematical addition (e.g., `num("hello", " world")` returns `"hello world"`). - Passing incompatible types (e.g., an integer and a string) will result in a `TypeError`. **Output Example**: The function returns a single value of the same or a promoted numeric type (e.g., adding an `int` and a `float` results in a `float`).</t>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>This function provides a straightforward way to perform addition. It accepts two parameters, `a` and `b`. Internally, it uses the standard Python addition operator (`+`) to compute the sum of these two values. The resulting sum is then returned as the output of the function. For example, if `a` is `5` and `b` is `10`, the function will compute `5 + 10` and return the value `15`.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>- The function is designed for numeric types like integers and floats. However, it will work with any two types that support the addition (`+`) operator, such as strings (for concatenation). - The function does not include any error handling. Passing incompatible types (e.g., an integer and a string) will result in a `TypeError`. **Output Example**: A numeric value representing the sum of the inputs.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>generate_random_integers(count, start, end)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>The `generate_random_integers` function returns a list containing a specified number of pseudo-random integers within a defined inclusive range.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Description | The total number of integers to generate in the list. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>This function provides a straightforward way to generate a list of random integers. The process is as follows: 1. **Input Validation**: The function first validates the `count` parameter. If `count` is a negative number, it raises a `ValueError` because it's impossible to generate a negative number of items. 2. **Range Correction**: It checks if the `start` value is greater than the `end` value. If it is, the function automatically swaps them. This ensures that `random.randint` receives a val...</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>- This function depends on Python's built-in `random` module. Ensure it is imported before use. - The `count` parameter must be a non-negative integer. - Both the `start` and `end` boundaries are inclusive, meaning they can appear in the output list. - If `start` is provided as a larger number than `end`, the function will automatically swap them and proceed without error. **Output Example**: A call to `generate_random_integers(5, 1, 10)` might produce a list like this:</t>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>The `generate_random_integers` function returns a list of a specified number of pseudo-random integers within a given inclusive range.</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Description | The number of integers to generate in the list. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>This function provides a convenient way to generate a list of random integers. It operates in three main steps: 1. **Input Validation**: It first checks if the `count` parameter is a non-negative number. If `count` is less than 0, it raises a `ValueError` to prevent invalid list creation. 2. **Range Correction**: The function ensures the range is valid by comparing `start` and `end`. If `start` is found to be greater than `end`, it automatically swaps their values. This allows the user to pro...</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>- This function requires the `random` module to be imported in the script. - A `ValueError` will be raised if the `count` argument is a negative integer. - The function is flexible with range ordering; if `start` &gt; `end`, the values will be swapped internally to form a valid range. - The returned integers are inclusive of both the `start` and `end` values. **Output Example**: A list of integers. The actual values will be random.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>fibonacci(n)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an efficient iterative approach.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>- `n`: `int` - The 0-indexed position in the Fibonacci sequence for which to find the corresponding number.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>This function calculates a Fibonacci number based on its index `n`. The Fibonacci sequence is a series of numbers where each number is the sum of the two preceding ones, usually starting with 0 and 1. The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError`, as the Fibonacci sequence is defined for non-negative integers. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequence (F...</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>- The input `n` must be a non-negative integer. Providing a negative integer will result in a `ValueError`. - The function uses a 0-indexed sequence. For example, `fibonacci(0)` returns `0`, `fibonacci(1)` returns `1`, and so on. - This iterative implementation is highly efficient in terms of memory and performance for large values of `n` compared to a naive recursive approach, as it avoids redundant calculations and deep recursion stacks. **Output Example**: The function returns a single int...</t>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>This function calculates a Fibonacci number based on its index `n`. It begins by validating the input, raising a `ValueError` if `n` is a negative number, as the Fibonacci sequence is not defined for negative indices. The function initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequence, F(0) and F(1). It then enters a `for` loop that iterates `n` times. In each iteration, the values of `a` and `b` are updated simultaneously. T...</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>- The input `n` must be a non-negative integer. Providing a negative integer will result in a `ValueError`. - The function uses a 0-indexed sequence, where `fibonacci(0)` returns `0`, `fibonacci(1)` returns `1`, and so on. - This iterative implementation is memory-efficient compared to a naive recursive approach, as it avoids deep recursion stacks. **Output Example**: A single integer representing the Fibonacci number at the specified index.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>choose_random_item(items)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>The `choose_random_item` function selects and returns a single random element from a given list of strings.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>- **`items`** (`List[str]`): A list of strings from which to choose a random item. This list must not be empty.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>This function provides a simple way to get a random item from a sequence. The core logic is implemented in two steps: 1. **Input Validation**: The function first checks if the provided `items` list is empty using the condition `if not items:`. If the list is empty, it raises a `ValueError` with the message "items must not be empty". This is a crucial safeguard to prevent the underlying `random.choice` function from failing, as it requires a non-empty sequence. 2. **Random Selection**: If the ...</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>- The input list `items` must contain at least one element. Providing an empty list will result in a `ValueError`. - This function depends on Python's built-in `random` module. Ensure that `import random` is present at the top of your script. - Each item in the list has an equal probability of being selected. **Output Example**: A single string from the input list. For an input of `["red", "green", "blue"]`, a possible return value is `"green"`.</t>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>The `choose_random_item` function selects and returns a single, random element from a given list of strings.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>- `items` (List[str]): A non-empty list of strings from which one item will be randomly selected.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>This function provides a simple way to pick one item uniformly at random from a sequence. The function first validates the input list `items`. It checks if the list is empty using `if not items:`. If the list is found to be empty, it raises a `ValueError` with the message "items must not be empty". This prevents errors from occurring in the subsequent `random.choice` call, which cannot operate on an empty sequence. If the list is not empty, the function proceeds to call `random.choice(items)`...</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>- The input list `items` must not be empty. Providing an empty list will raise a `ValueError`. - This function depends on Python's `random` module. Ensure it is imported in the script where this function is used (e.g., `import random`). - The selection is uniformly random, meaning every item in the list has an equal probability of being chosen. **Output Example**: A single string from the input list.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>shuffle_copy(items)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function creates and returns a randomly shuffled copy of a list of integers, leaving the original list unchanged.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>- `items` (`List[int]`): The list of integers to be copied and shuffled.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>This function provides a non-destructive way to shuffle a list. The logic proceeds in three steps: First, it creates a shallow copy of the input `items` list by calling `list(items)`. This ensures that any subsequent modifications do not affect the original list that was passed to the function. Next, it uses the `random.shuffle()` method to shuffle the elements of the newly created `copy` list in-place. This function rearranges the items in the list into a random order. Finally, the function ...</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>- The primary feature of this function is that it is non-mutating. The original list passed as the `items` parameter will remain in its original order after the function completes. - This function depends on Python's `random` module. Ensure that `import random` is present at the top of the script where this function is defined or called. - While the type hint specifies `List[int]`, the function's logic will work correctly with lists containing other data types (e.g., strings, floats, or mixed...</t>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list of integers without altering the original list.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>- `items` (`List[int]`): A list of integers to be copied and shuffled.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>This function provides a safe way to shuffle a list by ensuring the original data structure is not mutated. The process is straightforward: 1. A shallow copy of the input `items` list is created using the `list()` constructor. This new list is assigned to a local variable `copy`. This step is crucial for preserving the original list. 2. The `random.shuffle()` function is then called on the `copy`. The `random.shuffle()` method shuffles the elements of a sequence in-place. 3. Finally, the func...</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>- This function is non-destructive. The original list passed as the `items` parameter will remain unchanged after the function call. - The function depends on Python's `random` module. Ensure this module is imported (e.g., `import random`) before calling this function. - The output order is random and will be different on each execution. **Output Example**: A possible return value for an input of `[1, 2, 3, 4, 5]`.</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -465,7 +465,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>The `num` function calculates and returns the sum of two input arguments.</t>
+          <t>The `num` function calculates and returns the sum of two provided arguments.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to perform addition. It accepts two parameters, `a` and `b`. Internally, it uses the standard Python addition operator (`+`) to compute the sum of these two values. The resulting sum is then returned as the output of the function. For example, if `a` is `5` and `b` is `10`, the function will compute `5 + 10` and return the value `15`.</t>
+          <t>This function provides a straightforward way to perform addition. It accepts two parameters, `a` and `b`, which are expected to be numerical values (integers or floats). The core logic uses the standard Python addition operator (`+`) to compute the sum of `a` and `b`. The resulting value is then returned by the function. For example, if `a` is `5` and `b` is `10`, the function will compute `5 + 10` and return `15`.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>- The function is designed for numeric types like integers and floats. However, it will work with any two types that support the addition (`+`) operator, such as strings (for concatenation). - The function does not include any error handling. Passing incompatible types (e.g., an integer and a string) will result in a `TypeError`. **Output Example**: A numeric value representing the sum of the inputs.</t>
+          <t>- This function is designed primarily for numeric types like `int` and `float`. - If string values are passed as arguments, the function will perform string concatenation instead of mathematical addition (e.g., `num("hello", " world")` would return `"hello world"`). - Passing incompatible types (e.g., an integer and a string) will result in a `TypeError`. **Output Example**: A single numerical value representing the sum.</t>
         </is>
       </c>
     </row>
@@ -540,27 +540,27 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>generate_random_integers(count, start, end)</t>
+          <t>generate_random_integers</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>The `generate_random_integers` function returns a list of a specified number of pseudo-random integers within a given inclusive range.</t>
+          <t>The `generate_random_integers` function creates and returns a list of a specified number of pseudo-random integers within a given inclusive range.</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Description | The number of integers to generate in the list. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
+          <t>Description | The total number of integers to generate in the list. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a convenient way to generate a list of random integers. It operates in three main steps: 1. **Input Validation**: It first checks if the `count` parameter is a non-negative number. If `count` is less than 0, it raises a `ValueError` to prevent invalid list creation. 2. **Range Correction**: The function ensures the range is valid by comparing `start` and `end`. If `start` is found to be greater than `end`, it automatically swaps their values. This allows the user to pro...</t>
+          <t>This function provides a straightforward way to generate a list of random integers. It operates in three main steps: 1. **Input Validation**: It first checks if the `count` parameter is a non-negative number. If `count` is less than zero, it raises a `ValueError` to prevent invalid list creation. 2. **Range Correction**: The function ensures that the range defined by `start` and `end` is valid. If the provided `start` value is greater than the `end` value, it automatically swaps them. This al...</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>- This function requires the `random` module to be imported in the script. - A `ValueError` will be raised if the `count` argument is a negative integer. - The function is flexible with range ordering; if `start` &gt; `end`, the values will be swapped internally to form a valid range. - The returned integers are inclusive of both the `start` and `end` values. **Output Example**: A list of integers. The actual values will be random.</t>
+          <t>- The function requires the `random` module to be imported to work correctly. - A `ValueError` will be raised if the `count` argument is a negative integer. - If `start` is greater than `end`, their values will be swapped internally, so `generate_random_integers(5, 10, 1)` is equivalent to `generate_random_integers(5, 1, 10)`. - The `start` and `end` parameters are optional and have default values of `0` and `100` respectively. **Output Example**: The function returns a list of integers.</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>fibonacci(n)</t>
+          <t>fibonacci</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -580,17 +580,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
+          <t>- `n` (int): The 0-indexed index of the Fibonacci number to be computed.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>This function calculates a Fibonacci number based on its index `n`. It begins by validating the input, raising a `ValueError` if `n` is a negative number, as the Fibonacci sequence is not defined for negative indices. The function initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequence, F(0) and F(1). It then enters a `for` loop that iterates `n` times. In each iteration, the values of `a` and `b` are updated simultaneously. T...</t>
+          <t>This function calculates a number in the Fibonacci sequence, which starts with 0 and 1, and each subsequent number is the sum of the two preceding ones (e.g., 0, 1, 1, 2, 3, 5, ...). The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError` because the Fibonacci sequence is not defined for negative indices. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequence, F₀ and F₁. The c...</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>- The input `n` must be a non-negative integer. Providing a negative integer will result in a `ValueError`. - The function uses a 0-indexed sequence, where `fibonacci(0)` returns `0`, `fibonacci(1)` returns `1`, and so on. - This iterative implementation is memory-efficient compared to a naive recursive approach, as it avoids deep recursion stacks. **Output Example**: A single integer representing the Fibonacci number at the specified index.</t>
+          <t>- The input `n` must be a non-negative integer. The function will raise a `ValueError` for negative inputs. - The function uses a 0-indexed sequence, so `fibonacci(0)` returns `0`, `fibonacci(1)` returns `1`, and so on. - This iterative implementation is memory-efficient and avoids the recursion depth limits and performance issues associated with naive recursive solutions for large `n`. **Output Example**: The function returns a single integer representing the Fibonacci number at the specifie...</t>
         </is>
       </c>
     </row>
@@ -600,27 +600,27 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>choose_random_item(items)</t>
+          <t>choose_random_item</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single, random element from a given list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single, uniformly random item from a given list of strings.</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>- `items` (List[str]): A non-empty list of strings from which one item will be randomly selected.</t>
+          <t>- `items` (List[str]): A non-empty list of strings from which to choose a random item.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>This function provides a simple way to pick one item uniformly at random from a sequence. The function first validates the input list `items`. It checks if the list is empty using `if not items:`. If the list is found to be empty, it raises a `ValueError` with the message "items must not be empty". This prevents errors from occurring in the subsequent `random.choice` call, which cannot operate on an empty sequence. If the list is not empty, the function proceeds to call `random.choice(items)`...</t>
+          <t>This function provides a safe way to select a random element from a list. It begins by performing a validation check on the input `items`. If the provided list is empty (`if not items:`), the function immediately raises a `ValueError` to prevent runtime errors that would occur from attempting to choose from an empty sequence. If the list is not empty, the function proceeds to use the `random.choice()` method from Python's standard `random` library. This method takes the `items` list as an arg...</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will raise a `ValueError`. - This function depends on Python's `random` module. Ensure it is imported in the script where this function is used (e.g., `import random`). - The selection is uniformly random, meaning every item in the list has an equal probability of being chosen. **Output Example**: A single string from the input list.</t>
+          <t>- This function requires the input `items` to be a list of strings. - A `ValueError` will be raised if an empty list is passed as an argument. Ensure you handle this exception or validate the list's contents before calling the function. - The selection is uniformly random, meaning every item in the list has an equal chance of being chosen on any given call. - The function depends on Python's built-in `random` module. **Output Example**: The function returns a single string from the input list...</t>
         </is>
       </c>
     </row>
@@ -630,27 +630,27 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>shuffle_copy(items)</t>
+          <t>shuffle_copy</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list of integers without altering the original list.</t>
+          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list of integers without modifying the original list.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>- `items` (`List[int]`): A list of integers to be copied and shuffled.</t>
+          <t>* `items`: `List[int]` - The list of integers that will be copied and shuffled.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to shuffle a list by ensuring the original data structure is not mutated. The process is straightforward: 1. A shallow copy of the input `items` list is created using the `list()` constructor. This new list is assigned to a local variable `copy`. This step is crucial for preserving the original list. 2. The `random.shuffle()` function is then called on the `copy`. The `random.shuffle()` method shuffles the elements of a sequence in-place. 3. Finally, the func...</t>
+          <t>This function provides a safe and non-destructive way to shuffle the elements of a list. The core logic operates in three steps: 1. A new list named `copy` is created as a shallow copy of the input `items` list. This is achieved with the expression `list(items)`. This step is critical to ensure that the original list passed to the function remains unchanged. 2. The `random.shuffle(copy)` function is called. This function, part of Python's standard `random` module, shuffles the elements of the...</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>- This function is non-destructive. The original list passed as the `items` parameter will remain unchanged after the function call. - The function depends on Python's `random` module. Ensure this module is imported (e.g., `import random`) before calling this function. - The output order is random and will be different on each execution. **Output Example**: A possible return value for an input of `[1, 2, 3, 4, 5]`.</t>
+          <t>- This function is non-mutating. The original list passed as the `items` argument will not be altered. - The function requires the `random` module to be imported to use `random.shuffle`. - The order of the elements in the returned list is non-deterministic and will likely be different each time the function is called. **Output Example**: A possible return value for an input of `[1, 2, 3, 4, 5]` could be:</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -525,12 +525,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to perform addition. It accepts two parameters, `a` and `b`, which are expected to be numerical values (integers or floats). The core logic uses the standard Python addition operator (`+`) to compute the sum of `a` and `b`. The resulting value is then returned by the function. For example, if `a` is `5` and `b` is `10`, the function will compute `5 + 10` and return `15`.</t>
+          <t>This function performs a basic addition operation. It takes two parameters, `a` and `b`, which are expected to be numerical values (integers or floats). The core logic of the function is a single return statement that executes the expression `a + b`. The result of this addition is then immediately returned as the output of the function. For example, if `a` is `10` and `b` is `5`, the function will compute `10 + 5` and return the value `15`.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>- This function is designed primarily for numeric types like `int` and `float`. - If string values are passed as arguments, the function will perform string concatenation instead of mathematical addition (e.g., `num("hello", " world")` would return `"hello world"`). - Passing incompatible types (e.g., an integer and a string) will result in a `TypeError`. **Output Example**: A single numerical value representing the sum.</t>
+          <t>- The function relies on Python's `+` operator. Ensure that both `a` and `b` are of compatible types for addition. - If string values are passed as arguments, the function will perform string concatenation instead of mathematical addition. For example, `num("hello", "world")` would return `"helloworld"`. - Providing incompatible types (e.g., an integer and a string) will result in a `TypeError`. **Output Example**: If the inputs are `10` and `20`, the returned value will be: `30`</t>
         </is>
       </c>
     </row>
@@ -545,22 +545,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>The `generate_random_integers` function creates and returns a list of a specified number of pseudo-random integers within a given inclusive range.</t>
+          <t>The `generate_random_integers` function generates a list of a specified number of pseudo-random integers within a given inclusive range.</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Description | The total number of integers to generate in the list. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
+          <t>Description | The total number of integers to generate. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to generate a list of random integers. It operates in three main steps: 1. **Input Validation**: It first checks if the `count` parameter is a non-negative number. If `count` is less than zero, it raises a `ValueError` to prevent invalid list creation. 2. **Range Correction**: The function ensures that the range defined by `start` and `end` is valid. If the provided `start` value is greater than the `end` value, it automatically swaps them. This al...</t>
+          <t>This function provides a straightforward way to create a list of random integers. The process is as follows: 1. **Input Validation**: The function first checks if the `count` parameter is a non-negative number. If `count` is less than zero, it raises a `ValueError` to prevent invalid list creation. 2. **Range Correction**: It then compares the `start` and `end` parameters. If `start` is found to be greater than `end`, the function automatically swaps their values. This ensures that `random.ra...</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>- The function requires the `random` module to be imported to work correctly. - A `ValueError` will be raised if the `count` argument is a negative integer. - If `start` is greater than `end`, their values will be swapped internally, so `generate_random_integers(5, 10, 1)` is equivalent to `generate_random_integers(5, 1, 10)`. - The `start` and `end` parameters are optional and have default values of `0` and `100` respectively. **Output Example**: The function returns a list of integers.</t>
+          <t>- The `count` parameter must be a non-negative integer. Providing a negative value will raise a `ValueError`. - If the provided `start` value is greater than the `end` value, the function will automatically swap them to form a valid range. For instance, calling `generate_random_integers(5, 50, 10)` will be executed as if it were `generate_random_integers(5, 10, 50)`. - The generated integers are inclusive of both the `start` and `end` bounds. - This function depends on Python's built-in `rand...</t>
         </is>
       </c>
     </row>
@@ -575,22 +575,22 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an efficient iterative approach.</t>
+          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an iterative approach.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>- `n` (int): The 0-indexed index of the Fibonacci number to be computed.</t>
+          <t>- `n`: `int` - The 0-based index of the Fibonacci number to compute.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>This function calculates a number in the Fibonacci sequence, which starts with 0 and 1, and each subsequent number is the sum of the two preceding ones (e.g., 0, 1, 1, 2, 3, 5, ...). The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError` because the Fibonacci sequence is not defined for negative indices. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequence, F₀ and F₁. The c...</t>
+          <t>This function provides a memory-efficient way to calculate a number in the Fibonacci sequence. The logic proceeds as follows: 1. It first validates the input `n`. If `n` is a negative number, a `ValueError` is raised, as the Fibonacci sequence is not defined for negative indices. 2. Two variables, `a` and `b`, are initialized to `0` and `1` respectively. These represent the first two numbers in the sequence, F(0) and F(1). 3. A `for` loop iterates `n` times. In each iteration, the values of `...</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>- The input `n` must be a non-negative integer. The function will raise a `ValueError` for negative inputs. - The function uses a 0-indexed sequence, so `fibonacci(0)` returns `0`, `fibonacci(1)` returns `1`, and so on. - This iterative implementation is memory-efficient and avoids the recursion depth limits and performance issues associated with naive recursive solutions for large `n`. **Output Example**: The function returns a single integer representing the Fibonacci number at the specifie...</t>
+          <t>- The input `n` must be a non-negative integer. Providing a negative value will result in a `ValueError`. - The function uses 0-indexing, meaning `fibonacci(0)` returns the first element of the sequence, which is `0`. - This iterative implementation is efficient in terms of memory and performance for large values of `n` compared to a naive recursive approach, as it avoids redundant calculations and deep recursion stacks. **Output Example**: The function returns a single integer value.</t>
         </is>
       </c>
     </row>
@@ -605,22 +605,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single, uniformly random item from a given list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single random item from a given list of strings.</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>- `items` (List[str]): A non-empty list of strings from which to choose a random item.</t>
+          <t>- **`items`** (`List[str]`): A non-empty list of strings from which to choose a random item.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>This function provides a safe way to select a random element from a list. It begins by performing a validation check on the input `items`. If the provided list is empty (`if not items:`), the function immediately raises a `ValueError` to prevent runtime errors that would occur from attempting to choose from an empty sequence. If the list is not empty, the function proceeds to use the `random.choice()` method from Python's standard `random` library. This method takes the `items` list as an arg...</t>
+          <t>This function provides a simple way to get a random element from a list. The core logic is built around Python's `random.choice()` method. First, the function performs a validation check to ensure the input list `items` is not empty. If `items` is an empty list, the function will raise a `ValueError` with the message "items must not be empty". This prevents runtime errors from the underlying `random.choice()` function, which cannot operate on an empty sequence. If the list is valid (i.e., con...</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>- This function requires the input `items` to be a list of strings. - A `ValueError` will be raised if an empty list is passed as an argument. Ensure you handle this exception or validate the list's contents before calling the function. - The selection is uniformly random, meaning every item in the list has an equal chance of being chosen on any given call. - The function depends on Python's built-in `random` module. **Output Example**: The function returns a single string from the input list...</t>
+          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's `random` module. Ensure it is imported in the execution environment. - The selection is uniformly random, giving each item in the list an equal probability of being chosen. **Output Example**: The function returns a single string from the provided list.</t>
         </is>
       </c>
     </row>
@@ -635,22 +635,22 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list of integers without modifying the original list.</t>
+          <t>The `shuffle_copy` function creates and returns a shuffled copy of a given list, ensuring the original list remains unchanged.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>* `items`: `List[int]` - The list of integers that will be copied and shuffled.</t>
+          <t>- `items` (List[int]): A list of integers that you want to shuffle.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe and non-destructive way to shuffle the elements of a list. The core logic operates in three steps: 1. A new list named `copy` is created as a shallow copy of the input `items` list. This is achieved with the expression `list(items)`. This step is critical to ensure that the original list passed to the function remains unchanged. 2. The `random.shuffle(copy)` function is called. This function, part of Python's standard `random` module, shuffles the elements of the...</t>
+          <t>This function provides a safe way to shuffle a list without altering the original data structure. The process is straightforward and involves three main steps: 1. A shallow copy of the input `items` list is created using `list(items)`. This is a critical step to ensure that the original list passed to the function is not modified. The new copy is stored in a local variable named `copy`. 2. The `random.shuffle()` method is then called on the `copy`. This function shuffles the elements of the l...</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>- This function is non-mutating. The original list passed as the `items` argument will not be altered. - The function requires the `random` module to be imported to use `random.shuffle`. - The order of the elements in the returned list is non-deterministic and will likely be different each time the function is called. **Output Example**: A possible return value for an input of `[1, 2, 3, 4, 5]` could be:</t>
+          <t>- The primary benefit of this function is that it is non-mutating. The original list you provide as an argument will remain in its original order after the function completes. - This function relies on Python's `random` module. You must ensure that the `random` module is imported in the environment where this function is used. - While the type hint specifies `List[int]`, the function's logic will correctly handle lists containing elements of any data type (e.g., strings, floats, or mixed type...</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -515,22 +515,22 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>The `num` function calculates and returns the sum of two provided arguments.</t>
+          <t>The `num` function returns the result of applying the addition operator (`+`) to two input arguments.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Description | The first number to be added. | The second number to be added. |</t>
+          <t>Description | The first operand for the addition or concatenation operation. | The second operand, which must be of a type compatible with `a`. |</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>This function performs a basic addition operation. It takes two parameters, `a` and `b`, which are expected to be numerical values (integers or floats). The core logic of the function is a single return statement that executes the expression `a + b`. The result of this addition is then immediately returned as the output of the function. For example, if `a` is `10` and `b` is `5`, the function will compute `10 + 5` and return the value `15`.</t>
+          <t>This function takes two arguments, `a` and `b`, and computes their sum using the `+` operator. The behavior of the function is dependent on the data types of the input parameters. If `a` and `b` are numeric types (such as `int` or `float`), the function performs arithmetic addition and returns their numerical sum. If `a` and `b` are sequence types (such as `str` or `list`), the function performs concatenation and returns a new, combined sequence. The function does not include any internal typ...</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>- The function relies on Python's `+` operator. Ensure that both `a` and `b` are of compatible types for addition. - If string values are passed as arguments, the function will perform string concatenation instead of mathematical addition. For example, `num("hello", "world")` would return `"helloworld"`. - Providing incompatible types (e.g., an integer and a string) will result in a `TypeError`. **Output Example**: If the inputs are `10` and `20`, the returned value will be: `30`</t>
+          <t>- Ensure that both `a` and `b` are of compatible types that support the `+` operator. - The function will raise a `TypeError` if the operands are of unsupported types for addition, such as attempting to add a number to a string. - The order of parameters matters for non-commutative operations like string concatenation. For example, `num("a", "b")` returns `"ab"`, while `num("b", "a")` returns `"ba"`. **Output Example**: For numeric inputs `5` and `3`, the output would be:</t>
         </is>
       </c>
     </row>
@@ -550,17 +550,17 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Description | The total number of integers to generate. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
+          <t>Description | The number of random integers to generate. | The inclusive lower bound of the random number range. Defaults to `0`. | The inclusive upper bound of the random number range. Defaults to `100`. |</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to create a list of random integers. The process is as follows: 1. **Input Validation**: The function first checks if the `count` parameter is a non-negative number. If `count` is less than zero, it raises a `ValueError` to prevent invalid list creation. 2. **Range Correction**: It then compares the `start` and `end` parameters. If `start` is found to be greater than `end`, the function automatically swaps their values. This ensures that `random.ra...</t>
+          <t>This function provides a straightforward way to create a list of pseudo-random integers. It operates in a few distinct steps: First, it validates the `count` parameter. If `count` is a negative number, the function cannot produce a list of that length and will raise a `ValueError`. Next, it ensures the integrity of the numerical range. It checks if the `start` value is greater than the `end` value. If it is, the function automatically swaps them to ensure that `start` is always the lower boun...</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>- The `count` parameter must be a non-negative integer. Providing a negative value will raise a `ValueError`. - If the provided `start` value is greater than the `end` value, the function will automatically swap them to form a valid range. For instance, calling `generate_random_integers(5, 50, 10)` will be executed as if it were `generate_random_integers(5, 10, 50)`. - The generated integers are inclusive of both the `start` and `end` bounds. - This function depends on Python's built-in `rand...</t>
+          <t>- This function requires the `random` module to be imported to work correctly. - The `count` parameter must be a non-negative integer. Providing a negative value will result in a `ValueError`. - The function is inclusive of both the `start` and `end` values. - If the provided `start` value is greater than the `end` value, the function will automatically swap them to form a valid range. **Output Example**: A list of integers.</t>
         </is>
       </c>
     </row>
@@ -580,17 +580,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>- `n`: `int` - The 0-based index of the Fibonacci number to compute.</t>
+          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the value. Must be a non-negative integer.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>This function provides a memory-efficient way to calculate a number in the Fibonacci sequence. The logic proceeds as follows: 1. It first validates the input `n`. If `n` is a negative number, a `ValueError` is raised, as the Fibonacci sequence is not defined for negative indices. 2. Two variables, `a` and `b`, are initialized to `0` and `1` respectively. These represent the first two numbers in the sequence, F(0) and F(1). 3. A `for` loop iterates `n` times. In each iteration, the values of `...</t>
+          <t>This function calculates a Fibonacci number based on its index `n`. The logic begins by handling invalid input; if `n` is a negative number, a `ValueError` is raised. The function initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the Fibonacci sequence (F₀ and F₁). It then enters a `for` loop that iterates `n` times. In each iteration, the values of `a` and `b` are updated using tuple assignment: `a, b = b, a + b`. This operation eff...</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>- The input `n` must be a non-negative integer. Providing a negative value will result in a `ValueError`. - The function uses 0-indexing, meaning `fibonacci(0)` returns the first element of the sequence, which is `0`. - This iterative implementation is efficient in terms of memory and performance for large values of `n` compared to a naive recursive approach, as it avoids redundant calculations and deep recursion stacks. **Output Example**: The function returns a single integer value.</t>
+          <t>- The input `n` must be a non-negative integer. The function will raise a `ValueError` for negative inputs. - The function is 0-indexed, meaning `fibonacci(0)` returns the first element of the sequence, `0`. - This iterative implementation is memory-efficient compared to a naive recursive approach, as it avoids a deep call stack. **Output Example**: A single integer representing the Fibonacci number at the specified index.</t>
         </is>
       </c>
     </row>
@@ -605,22 +605,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single random item from a given list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single, uniformly random item from a given list of strings.</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>- **`items`** (`List[str]`): A non-empty list of strings from which to choose a random item.</t>
+          <t>- `items` (List[str]): A list of strings from which to choose. This list must not be empty.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>This function provides a simple way to get a random element from a list. The core logic is built around Python's `random.choice()` method. First, the function performs a validation check to ensure the input list `items` is not empty. If `items` is an empty list, the function will raise a `ValueError` with the message "items must not be empty". This prevents runtime errors from the underlying `random.choice()` function, which cannot operate on an empty sequence. If the list is valid (i.e., con...</t>
+          <t>This function provides a safe way to select a random element from a list. The logic proceeds as follows: 1. It first performs a validation check on the input list `items`. The condition `if not items:` evaluates to `True` if the list is empty. 2. If the list is found to be empty, the function immediately stops execution and raises a `ValueError` with the message "items must not be empty". This prevents potential errors from the underlying `random.choice` method, which requires a non-empty seq...</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's `random` module. Ensure it is imported in the execution environment. - The selection is uniformly random, giving each item in the list an equal probability of being chosen. **Output Example**: The function returns a single string from the provided list.</t>
+          <t>- The input list `items` must contain at least one element. Providing an empty list will raise a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in your script (e.g., `import random`). - The selection is uniformly random, meaning every item in the list has an equal chance of being chosen on any given call. **Output Example**: A single string from the input list. `"banana"`</t>
         </is>
       </c>
     </row>
@@ -635,22 +635,22 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function creates and returns a shuffled copy of a given list, ensuring the original list remains unchanged.</t>
+          <t>The `shuffle_copy` function returns a new list containing a shuffled version of the elements from the input list, without modifying the original list.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>- `items` (List[int]): A list of integers that you want to shuffle.</t>
+          <t>- **items** (`List[int]`): A list of integers to be shuffled.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to shuffle a list without altering the original data structure. The process is straightforward and involves three main steps: 1. A shallow copy of the input `items` list is created using `list(items)`. This is a critical step to ensure that the original list passed to the function is not modified. The new copy is stored in a local variable named `copy`. 2. The `random.shuffle()` method is then called on the `copy`. This function shuffles the elements of the l...</t>
+          <t>This function provides a safe way to shuffle a list by operating on a copy rather than the original. The process is as follows: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is a critical step to ensure that the original list remains unchanged, adhering to the non-mutating principle of the function. 2. The `random.shuffle()` method is then called on this `copy`. This method shuffles the elements of the list in-place, rearranging them into a random ord...</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>- The primary benefit of this function is that it is non-mutating. The original list you provide as an argument will remain in its original order after the function completes. - This function relies on Python's `random` module. You must ensure that the `random` module is imported in the environment where this function is used. - While the type hint specifies `List[int]`, the function's logic will correctly handle lists containing elements of any data type (e.g., strings, floats, or mixed type...</t>
+          <t>- This function is non-mutating. It will always return a new list and will not alter the original list provided as the `items` parameter. - The function relies on the `random` module. Ensure that `import random` is present in the file where this function is used. - Although the type hint specifies `List[int]`, the underlying logic will work correctly with lists containing elements of any type (e.g., strings, floats, or mixed types). **Output Example**: The function returns a `list` where the ...</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Documentation" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,44 +461,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Function No</t>
+          <t>Item No</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Function Name</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Parameters</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Usage Notes</t>
         </is>
@@ -510,27 +516,32 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
           <t>num(a, b)</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>The `num` function returns the result of applying the addition operator (`+`) to two input arguments.</t>
-        </is>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Description | The first operand for the addition or concatenation operation. | The second operand, which must be of a type compatible with `a`. |</t>
+          <t>The `num` function calculates and returns the sum of two provided numbers.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>This function takes two arguments, `a` and `b`, and computes their sum using the `+` operator. The behavior of the function is dependent on the data types of the input parameters. If `a` and `b` are numeric types (such as `int` or `float`), the function performs arithmetic addition and returns their numerical sum. If `a` and `b` are sequence types (such as `str` or `list`), the function performs concatenation and returns a new, combined sequence. The function does not include any internal typ...</t>
+          <t>Description | The first number to be used in the addition. | The second number to be used in the addition. |</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>- Ensure that both `a` and `b` are of compatible types that support the `+` operator. - The function will raise a `TypeError` if the operands are of unsupported types for addition, such as attempting to add a number to a string. - The order of parameters matters for non-commutative operations like string concatenation. For example, `num("a", "b")` returns `"ab"`, while `num("b", "a")` returns `"ba"`. **Output Example**: For numeric inputs `5` and `3`, the output would be:</t>
+          <t>This function provides a straightforward way to perform addition. It accepts two arguments, `a` and `b`, and computes their sum using the `+` operator. The function then returns the resulting value. While designed for numeric types like integers and floats, the `+` operator's behavior in Python means it will also concatenate other types that support it, such as strings. For example, if `a` is `5` and `b` is `10`, the function will return `15`.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>- For mathematical addition, ensure that both `a` and `b` are numeric types (e.g., `int` or `float`). - If string values are passed as arguments, the function will perform string concatenation instead of arithmetic addition (e.g., `num("hello", "world")` would return `"helloworld"`). **Output Example**: A numeric sum.</t>
         </is>
       </c>
     </row>
@@ -540,27 +551,32 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>generate_random_integers</t>
+          <t>FunctionDef</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>The `generate_random_integers` function generates a list of a specified number of pseudo-random integers within a given inclusive range.</t>
+          <t>num</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Description | The number of random integers to generate. | The inclusive lower bound of the random number range. Defaults to `0`. | The inclusive upper bound of the random number range. Defaults to `100`. |</t>
+          <t>The `num` function is a placeholder that accepts two arguments but performs no operations and returns `None`.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to create a list of pseudo-random integers. It operates in a few distinct steps: First, it validates the `count` parameter. If `count` is a negative number, the function cannot produce a list of that length and will raise a `ValueError`. Next, it ensures the integrity of the numerical range. It checks if the `start` value is greater than the `end` value. If it is, the function automatically swaps them to ensure that `start` is always the lower boun...</t>
+          <t>Description | The first input parameter. It is not used within the function's body. | The second input parameter. It is not used within the function's body. |</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>- This function requires the `random` module to be imported to work correctly. - The `count` parameter must be a non-negative integer. Providing a negative value will result in a `ValueError`. - The function is inclusive of both the `start` and `end` values. - If the provided `start` value is greater than the `end` value, the function will automatically swap them to form a valid range. **Output Example**: A list of integers.</t>
+          <t>The `num` function is defined to accept two parameters, `a` and `b`. The body of the function is empty, meaning it contains no implementation or logic. Consequently, when called, the function executes nothing and does not perform any operations on the input arguments. In Python, a function that does not have an explicit `return` statement will implicitly return `None` upon completion.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>- This function can be called with any two arguments, but they will have no effect on the outcome. - The function will always return `None`. - It likely serves as a stub or placeholder for functionality that is intended to be implemented in the future.</t>
         </is>
       </c>
     </row>
@@ -570,27 +586,32 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>fibonacci</t>
+          <t>FunctionDef</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an iterative approach.</t>
+          <t>generate_random_integers</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the value. Must be a non-negative integer.</t>
+          <t>The `generate_random_integers` function creates and returns a list of a specified number of pseudo-random integers within a given inclusive range.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>This function calculates a Fibonacci number based on its index `n`. The logic begins by handling invalid input; if `n` is a negative number, a `ValueError` is raised. The function initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the Fibonacci sequence (F₀ and F₁). It then enters a `for` loop that iterates `n` times. In each iteration, the values of `a` and `b` are updated using tuple assignment: `a, b = b, a + b`. This operation eff...</t>
+          <t>Description | The total number of integers to generate for the list. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>- The input `n` must be a non-negative integer. The function will raise a `ValueError` for negative inputs. - The function is 0-indexed, meaning `fibonacci(0)` returns the first element of the sequence, `0`. - This iterative implementation is memory-efficient compared to a naive recursive approach, as it avoids a deep call stack. **Output Example**: A single integer representing the Fibonacci number at the specified index.</t>
+          <t>This function provides a convenient way to generate a list of random integers. The logic proceeds as follows: 1. It first validates the `count` parameter. If `count` is a negative number, the function raises a `ValueError` because it's not possible to generate a negative quantity of items. 2. Next, it ensures the range is valid by checking if the `start` value is greater than the `end` value. If it is, the function automatically swaps them. This makes the function robust, as the caller does n...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>- This function depends on Python's built-in `random` module. Ensure it is imported in your script before calling this function. - The `count` parameter must be a non-negative integer (`&gt;= 0`). - Both the `start` and `end` boundaries are inclusive, meaning they can appear in the output list. - If `start` is provided with a value greater than `end`, the function will automatically swap them to form a valid range. **Output Example**: A possible return value for `generate_random_integers(5, 1, 1...</t>
         </is>
       </c>
     </row>
@@ -600,27 +621,32 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>choose_random_item</t>
+          <t>FunctionDef</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single, uniformly random item from a given list of strings.</t>
+          <t>generate_random_integers</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>- `items` (List[str]): A list of strings from which to choose. This list must not be empty.</t>
+          <t>The `generate_random_integers` function creates and returns a list containing a specified number of random integers within a defined inclusive range.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>This function provides a safe way to select a random element from a list. The logic proceeds as follows: 1. It first performs a validation check on the input list `items`. The condition `if not items:` evaluates to `True` if the list is empty. 2. If the list is found to be empty, the function immediately stops execution and raises a `ValueError` with the message "items must not be empty". This prevents potential errors from the underlying `random.choice` method, which requires a non-empty seq...</t>
+          <t>Description | The total number of random integers to generate and include in the output list. | The inclusive lower bound for the random number generation. This is an optional parameter with a default value of `0`. | The inclusive upper bound for the random number generation. This is an optional parameter with a default value of `100`. |</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>- The input list `items` must contain at least one element. Providing an empty list will raise a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in your script (e.g., `import random`). - The selection is uniformly random, meaning every item in the list has an equal chance of being chosen on any given call. **Output Example**: A single string from the input list. `"banana"`</t>
+          <t>This function provides a straightforward way to generate a collection of random integers. It operates by iterating `count` times. In each iteration, it produces a single random integer that falls between the `start` and `end` values, inclusive of both endpoints. These generated integers are collected into a list, which is the final return value of the function. The function signature includes default values for `start` (0) and `end` (100), making it convenient for generating common ranges of ...</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>- The value of `start` must be less than or equal to the value of `end`. If `start` is greater than `end`, the underlying `random.randint()` function will raise a `ValueError`. - The function returns a `List[int]` with a length equal to the `count` argument. - The output is non-deterministic; each call to the function will produce a different list of random integers.</t>
         </is>
       </c>
     </row>
@@ -630,27 +656,207 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>fibonacci</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an efficient iterative method.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>This function calculates a specific number in the Fibonacci sequence, which is a series where each number is the sum of the two preceding ones, starting from 0 and 1. The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError` because the Fibonacci sequence is not defined for negative indices. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequence, F₀ and F₁. The core logic reside...</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>- The function expects a non-negative integer for the `n` parameter. A `ValueError` will be raised for negative inputs. - The sequence is 0-indexed, meaning `fibonacci(0)` returns the first number (0), `fibonacci(1)` returns the second (1), and so on. - This implementation is iterative and avoids the performance issues of deep recursion, making it suitable for calculating larger Fibonacci numbers efficiently. **Output Example**: A single integer representing the Fibonacci number at the specif...</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>fibonacci</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>The `fibonacci` function is a placeholder intended to calculate the nth number in the Fibonacci sequence.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>- `n` (int): The index (position) in the Fibonacci sequence to be calculated.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>This function is defined to compute a number from the Fibonacci sequence based on its position `n`. The Fibonacci sequence is a series of numbers where each number is the sum of the two preceding ones, typically starting with 0 and 1. As currently implemented, the function is a stub with an empty body. It accepts an integer `n` as input but does not contain any logic to perform the calculation. Consequently, it does not explicitly return a value. In Python, a function that does not have a `re...</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>- This function is currently unimplemented. Calling it will not perform any calculation. - The function will implicitly return `None` for any input value. - The parameter `n` is intended to be a non-negative integer representing the position in the sequence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>choose_random_item</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>The `choose_random_item` function selects and returns a single, uniformly random element from a given list of strings.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>- **`items`** (`List[str]`): A list of strings from which a random item will be chosen. This list cannot be empty.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>This function provides a safe way to pick a random item from a list. The logic proceeds as follows: 1. It first performs a validation check to see if the input list `items` is empty using the condition `if not items:`. 2. If the list is empty, the function raises a `ValueError` with the message "items must not be empty". This is a crucial guard clause to prevent the underlying `random.choice` function from failing, as it cannot operate on an empty sequence. 3. If the list is not empty, the fu...</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's `random` module. Ensure that `import random` is present in the scope where this function is defined or used. - The function is type-hinted to accept a list of strings (`List[str]`) and return a single string (`str`). **Output Example**: The function returns a single string from the input list. For an input of `["red", "green", "blue"]`, a possible return value...</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>choose_random_item</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>The `choose_random_item` function randomly selects and returns a single string element from a given list of strings.</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>- **`items`** (`List[str]`): A list of strings from which one item will be randomly chosen.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>This function provides a straightforward way to get a random element from a list. It takes a single argument, `items`, which is expected to be a list of strings. Internally, the function utilizes Python's `random` module, specifically the `random.choice()` method. This method is designed to pick a random item from a non-empty sequence. The function then returns the selected string. If the provided `items` list is empty, calling this function will result in an `IndexError` because `random.choi...</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>- The input list `items` must not be empty. Passing an empty list will raise an `IndexError`. - The function is dependent on Python's `random` module. - The selection is pseudo-random and its properties depend on the underlying random number generator used by the `random` module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>shuffle_copy</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function returns a new list containing a shuffled version of the elements from the input list, without modifying the original list.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>- **items** (`List[int]`): A list of integers to be shuffled.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to shuffle a list by operating on a copy rather than the original. The process is as follows: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is a critical step to ensure that the original list remains unchanged, adhering to the non-mutating principle of the function. 2. The `random.shuffle()` method is then called on this `copy`. This method shuffles the elements of the list in-place, rearranging them into a random ord...</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>- This function is non-mutating. It will always return a new list and will not alter the original list provided as the `items` parameter. - The function relies on the `random` module. Ensure that `import random` is present in the file where this function is used. - Although the type hint specifies `List[int]`, the underlying logic will work correctly with lists containing elements of any type (e.g., strings, floats, or mixed types). **Output Example**: The function returns a `list` where the ...</t>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original input list is not altered.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>- `items`: `List[int]` - A list of integers that you want to shuffle.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>This function provides a safe way to shuffle a list without side effects. The process is straightforward: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is a crucial step that isolates the operation from the original data. 2. The `random.shuffle()` function is then called on this `copy`. `random.shuffle()` shuffles the elements of a list in-place. 3. Finally, the function returns the modified `copy`, which now contains the same elements as the original...</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>- This function requires the `random` module to be imported to use `random.shuffle()`. - The primary benefit of this function is its non-mutating behavior. It is a "safe" alternative to calling `random.shuffle()` directly on a list that you need to preserve. - Although the type hint specifies `List[int]`, the function will work correctly with lists containing elements of any type (e.g., strings, floats, or mixed types). **Output Example**: The output is a new list with the same elements as th...</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>shuffle_copy</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>The `shuffle_copy` function creates and returns a new list containing the same elements as the input list but arranged in a random order.</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>- `items`: A list of integers (`List[int]`) that will be shuffled. The original list provided to this parameter remains unmodified.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>This function provides a non-destructive way to shuffle a list. It operates in two main steps: 1. **Create a Copy:** It first creates a shallow copy of the input `items` list. This step is crucial as it ensures that the original list passed by the user is not altered. 2. **Shuffle the Copy:** It then shuffles the elements of this newly created copy in-place, randomizing their order. A common implementation would use an algorithm like the Fisher-Yates shuffle. Finally, the function returns the...</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>- The primary feature of this function is that it is **non-destructive**. The original list you pass as an argument will not be changed. - The function returns a **new list**. You must assign the result to a variable to access the shuffled sequence. - Due to the nature of randomization, calling the function multiple times with the identical input list will likely produce different output lists each time. - Although the type hint specifies `List[int]`, the underlying logic works for lists cont...</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -526,22 +526,22 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `num` function calculates and returns the sum of two provided numbers.</t>
+          <t>The `num` function calculates and returns the sum of two provided arguments.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Description | The first number to be used in the addition. | The second number to be used in the addition. |</t>
+          <t>Description | The first number to be added. | The second number to be added. |</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to perform addition. It accepts two arguments, `a` and `b`, and computes their sum using the `+` operator. The function then returns the resulting value. While designed for numeric types like integers and floats, the `+` operator's behavior in Python means it will also concatenate other types that support it, such as strings. For example, if `a` is `5` and `b` is `10`, the function will return `15`.</t>
+          <t>This function provides a straightforward way to perform addition. It accepts two parameters, `a` and `b`, which are expected to be numerical values (integers or floating-point numbers). The core logic of the function uses the `+` operator to compute the sum of `a` and `b`. The resulting value is then returned to the caller. For example, if `a` is `10` and `b` is `5`, the function will compute `10 + 5` and return `15`.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- For mathematical addition, ensure that both `a` and `b` are numeric types (e.g., `int` or `float`). - If string values are passed as arguments, the function will perform string concatenation instead of arithmetic addition (e.g., `num("hello", "world")` would return `"helloworld"`). **Output Example**: A numeric sum.</t>
+          <t>Important points to consider when using this function: - The function relies on Python's `+` operator. Ensure that both input arguments are of types that support addition (e.g., `int`, `float`). Passing incompatible types (like an `int` and a `NoneType`) will result in a `TypeError`. - If strings are passed as arguments, the function will perform string concatenation instead of mathematical addition. For example, `num("hello", "world")` would return `"helloworld"`. - The data type of the retu...</t>
         </is>
       </c>
     </row>
@@ -571,12 +571,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>The `num` function is defined to accept two parameters, `a` and `b`. The body of the function is empty, meaning it contains no implementation or logic. Consequently, when called, the function executes nothing and does not perform any operations on the input arguments. In Python, a function that does not have an explicit `return` statement will implicitly return `None` upon completion.</t>
+          <t>The `num` function is defined with two parameters, `a` and `b`. The function body is currently empty, meaning it contains no logic or operations. Consequently, the function does not utilize the input parameters for any computation. In Python, a function that does not have an explicit `return` statement will implicitly return the `None` object.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- This function can be called with any two arguments, but they will have no effect on the outcome. - The function will always return `None`. - It likely serves as a stub or placeholder for functionality that is intended to be implemented in the future.</t>
+          <t>- This function currently acts as a stub or placeholder and lacks any functional implementation. - Calling this function with any arguments will always result in a return value of `None`. - It is likely intended for future development where functionality will be added.</t>
         </is>
       </c>
     </row>
@@ -596,22 +596,22 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>The `generate_random_integers` function creates and returns a list of a specified number of pseudo-random integers within a given inclusive range.</t>
+          <t>The `generate_random_integers` function generates a list of a specified number of pseudo-random integers within a given inclusive range.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Description | The total number of integers to generate for the list. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
+          <t>Description | The number of random integers to generate. This value must be non-negative. | The inclusive lower bound of the random number range. Defaults to `0`. | The inclusive upper bound of the random number range. Defaults to `100`. |</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function provides a convenient way to generate a list of random integers. The logic proceeds as follows: 1. It first validates the `count` parameter. If `count` is a negative number, the function raises a `ValueError` because it's not possible to generate a negative quantity of items. 2. Next, it ensures the range is valid by checking if the `start` value is greater than the `end` value. If it is, the function automatically swaps them. This makes the function robust, as the caller does n...</t>
+          <t>This function provides a convenient way to generate a list of pseudo-random integers. It operates in a few distinct steps: 1. **Input Validation**: The function first checks if the `count` parameter is a negative number. If it is, a `ValueError` is raised, as it's impossible to generate a negative quantity of numbers. 2. **Range Correction**: It then verifies if the `start` value is greater than the `end` value. If this condition is true, the function automatically swaps the two values. This ...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- This function depends on Python's built-in `random` module. Ensure it is imported in your script before calling this function. - The `count` parameter must be a non-negative integer (`&gt;= 0`). - Both the `start` and `end` boundaries are inclusive, meaning they can appear in the output list. - If `start` is provided with a value greater than `end`, the function will automatically swap them to form a valid range. **Output Example**: A possible return value for `generate_random_integers(5, 1, 1...</t>
+          <t>- The function requires the `random` module to be imported. - A `ValueError` will be raised if a negative value is passed for the `count` parameter. - The range defined by `start` and `end` is inclusive, meaning both `start` and `end` are potential values in the output list. - If `start` is greater than `end`, the function will automatically swap them and proceed without error. **Output Example**: A list of integers. The actual numbers will vary with each execution due to their random nature.</t>
         </is>
       </c>
     </row>
@@ -631,22 +631,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The `generate_random_integers` function creates and returns a list containing a specified number of random integers within a defined inclusive range.</t>
+          <t>The `generate_random_integers` function generates a list containing a specified number of random integers within a given inclusive range.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Description | The total number of random integers to generate and include in the output list. | The inclusive lower bound for the random number generation. This is an optional parameter with a default value of `0`. | The inclusive upper bound for the random number generation. This is an optional parameter with a default value of `100`. |</t>
+          <t>Description | The total number of random integers to generate. This is a required argument. | The inclusive lower bound of the random number range. Defaults to `0`. | The inclusive upper bound of the random number range. Defaults to `100`. |</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to generate a collection of random integers. It operates by iterating `count` times. In each iteration, it produces a single random integer that falls between the `start` and `end` values, inclusive of both endpoints. These generated integers are collected into a list, which is the final return value of the function. The function signature includes default values for `start` (0) and `end` (100), making it convenient for generating common ranges of ...</t>
+          <t>This function produces a list of pseudo-random integers. The quantity of integers in the resulting list is determined by the `count` parameter. Each integer in the list is generated within the numerical range defined by the `start` and `end` parameters. This range is inclusive, meaning that the values of `start` and `end` themselves are potential outcomes. If the `start` and `end` parameters are not explicitly provided, the function uses a default range from `0` to `100`. The core logic invol...</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- The value of `start` must be less than or equal to the value of `end`. If `start` is greater than `end`, the underlying `random.randint()` function will raise a `ValueError`. - The function returns a `List[int]` with a length equal to the `count` argument. - The output is non-deterministic; each call to the function will produce a different list of random integers.</t>
+          <t>- The value for `start` must be less than or equal to the value for `end`. If `start` is greater than `end`, the underlying random number generation will raise a `ValueError`. - The `count` parameter should be a non-negative integer. If `count` is `0`, an empty list will be returned. - The numbers generated are pseudo-random and should not be used for cryptographic purposes. For security-sensitive applications, consider using the `secrets` module.</t>
         </is>
       </c>
     </row>
@@ -666,22 +666,22 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an efficient iterative method.</t>
+          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an iterative approach.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
+          <t>- `n`: `int` - The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>This function calculates a specific number in the Fibonacci sequence, which is a series where each number is the sum of the two preceding ones, starting from 0 and 1. The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError` because the Fibonacci sequence is not defined for negative indices. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequence, F₀ and F₁. The core logic reside...</t>
+          <t>This function calculates a Fibonacci number based on its index `n`. The logic begins by validating the input. If `n` is a negative number, a `ValueError` is raised, as the Fibonacci sequence is not defined for negative indices. The function initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the Fibonacci sequence (F₀ and F₁). It then enters a `for` loop that iterates `n` times. In each iteration, the values of `a` and `b` are updated ...</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>- The function expects a non-negative integer for the `n` parameter. A `ValueError` will be raised for negative inputs. - The sequence is 0-indexed, meaning `fibonacci(0)` returns the first number (0), `fibonacci(1)` returns the second (1), and so on. - This implementation is iterative and avoids the performance issues of deep recursion, making it suitable for calculating larger Fibonacci numbers efficiently. **Output Example**: A single integer representing the Fibonacci number at the specif...</t>
+          <t>- The input `n` must be a non-negative integer. Providing a negative value will result in a `ValueError`. - The function uses a 0-indexed sequence. For example, `fibonacci(0)` returns the first number (`0`), and `fibonacci(1)` returns the second number (`1`). - This iterative implementation is memory-efficient and avoids the recursion depth issues that can occur with naive recursive solutions for large values of `n`. **Output Example**: A possible return value for a valid input.</t>
         </is>
       </c>
     </row>
@@ -701,22 +701,22 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>The `fibonacci` function is a placeholder intended to calculate the nth number in the Fibonacci sequence.</t>
+          <t>The `fibonacci` function calculates the n-th number in the Fibonacci sequence.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>- `n` (int): The index (position) in the Fibonacci sequence to be calculated.</t>
+          <t>- `n` (int): A non-negative integer representing the position (index) in the Fibonacci sequence. The sequence is 0-indexed.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>This function is defined to compute a number from the Fibonacci sequence based on its position `n`. The Fibonacci sequence is a series of numbers where each number is the sum of the two preceding ones, typically starting with 0 and 1. As currently implemented, the function is a stub with an empty body. It accepts an integer `n` as input but does not contain any logic to perform the calculation. Consequently, it does not explicitly return a value. In Python, a function that does not have a `re...</t>
+          <t>This function computes a number in the Fibonacci sequence, which is a series of numbers where each number is the sum of the two preceding ones. The sequence implemented by this function starts with 0 and 1. The function handles the base cases first: - If `n` is 0 or a negative number, it returns 0. - If `n` is 1, it returns 1. For any `n` greater than 1, the function iteratively calculates the value. It initializes two variables, `a` and `b`, to the first two numbers of the sequence (0 and 1)...</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>- This function is currently unimplemented. Calling it will not perform any calculation. - The function will implicitly return `None` for any input value. - The parameter `n` is intended to be a non-negative integer representing the position in the sequence.</t>
+          <t>- The input `n` must be an integer. The function is designed for non-negative integers. - If a negative integer is provided for `n`, the function will return 0. - Be aware that Fibonacci numbers grow exponentially. While Python's integers can handle arbitrary size, calculations for extremely large values of `n` can be computationally intensive and result in very large numbers.</t>
         </is>
       </c>
     </row>
@@ -736,22 +736,22 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single, uniformly random element from a given list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single, uniformly random item from a given list of strings.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>- **`items`** (`List[str]`): A list of strings from which a random item will be chosen. This list cannot be empty.</t>
+          <t>* **items** (`List[str]`): A non-empty list of strings from which to choose a random item.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to pick a random item from a list. The logic proceeds as follows: 1. It first performs a validation check to see if the input list `items` is empty using the condition `if not items:`. 2. If the list is empty, the function raises a `ValueError` with the message "items must not be empty". This is a crucial guard clause to prevent the underlying `random.choice` function from failing, as it cannot operate on an empty sequence. 3. If the list is not empty, the fu...</t>
+          <t>This function provides a simple way to get a random element from a list. The logic proceeds in two main steps: 1. **Validation**: The function first checks if the provided `items` list is empty using the condition `if not items:`. This is a crucial safeguard to ensure the function operates correctly. If the list is empty, it raises a `ValueError` with the message "items must not be empty", preventing the program from proceeding with invalid input. 2. **Random Selection**: If the list is not e...</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's `random` module. Ensure that `import random` is present in the scope where this function is defined or used. - The function is type-hinted to accept a list of strings (`List[str]`) and return a single string (`str`). **Output Example**: The function returns a single string from the input list. For an input of `["red", "green", "blue"]`, a possible return value...</t>
+          <t>Important points to consider when using this function: - The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's `random` module. Ensure it is imported in the scope where this function is defined or called. - The selection is uniformly random, meaning every item in the list has an equal probability of being chosen. **Output Example**: The function returns a single string. If the input is `['apple', 'banana', 'cherry'...</t>
         </is>
       </c>
     </row>
@@ -771,22 +771,22 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function randomly selects and returns a single string element from a given list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single, randomly chosen element from a given list of strings.</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>- **`items`** (`List[str]`): A list of strings from which one item will be randomly chosen.</t>
+          <t>- `items` (`List[str]`): A list of strings from which one item will be randomly selected.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to get a random element from a list. It takes a single argument, `items`, which is expected to be a list of strings. Internally, the function utilizes Python's `random` module, specifically the `random.choice()` method. This method is designed to pick a random item from a non-empty sequence. The function then returns the selected string. If the provided `items` list is empty, calling this function will result in an `IndexError` because `random.choi...</t>
+          <t>This function is designed to perform a random selection from a collection of items. It accepts a single argument, `items`, which is a list of strings. The intended logic is to use a random selection mechanism to pick one of the strings from this list. The standard Python approach for this task is to use the `random.choice()` function from the built-in `random` module. This method takes a non-empty sequence (like a list) and returns a randomly selected element. A complete implementation would ...</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Passing an empty list will raise an `IndexError`. - The function is dependent on Python's `random` module. - The selection is pseudo-random and its properties depend on the underlying random number generator used by the `random` module.</t>
+          <t>- The input list `items` must not be empty. Providing an empty list will cause a `random.choice()` call to raise an `IndexError`. - The selection is pseudo-random, meaning the sequence of chosen items is determined by the initial seed of the random number generator. - While the type hint specifies `List[str]`, the underlying `random.choice()` function works with any non-empty sequence (e.g., list of integers, tuples, etc.).</t>
         </is>
       </c>
     </row>
@@ -806,22 +806,22 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original input list is not altered.</t>
+          <t>The `shuffle_copy` function returns a shuffled copy of a given list of integers without modifying the original list.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>- `items`: `List[int]` - A list of integers that you want to shuffle.</t>
+          <t>- `items` (List[int]): A list of integers to be copied and shuffled.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to shuffle a list without side effects. The process is straightforward: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is a crucial step that isolates the operation from the original data. 2. The `random.shuffle()` function is then called on this `copy`. `random.shuffle()` shuffles the elements of a list in-place. 3. Finally, the function returns the modified `copy`, which now contains the same elements as the original...</t>
+          <t>This function provides a safe way to shuffle a list by operating on a copy rather than the original data. The process is as follows: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This step is crucial as it ensures that the original list passed to the function remains unchanged. 2. The `random.shuffle()` method is then called on the `copy`. This function shuffles the elements of the `copy` list in-place, rearranging them into a random order. 3. Finally, the...</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>- This function requires the `random` module to be imported to use `random.shuffle()`. - The primary benefit of this function is its non-mutating behavior. It is a "safe" alternative to calling `random.shuffle()` directly on a list that you need to preserve. - Although the type hint specifies `List[int]`, the function will work correctly with lists containing elements of any type (e.g., strings, floats, or mixed types). **Output Example**: The output is a new list with the same elements as th...</t>
+          <t>- This function is non-mutating, meaning the original list you pass as an argument will not be altered. - The function depends on Python's built-in `random` module. Ensure this module is available in the environment. - The order of the elements in the returned list is non-deterministic and will be different on each execution. **Output Example**: A new list containing the same integers as the input list, but in a random order. For an input of `[1, 2, 3, 4, 5]`, a possible output could be `[3, ...</t>
         </is>
       </c>
     </row>
@@ -846,17 +846,17 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>- `items`: A list of integers (`List[int]`) that will be shuffled. The original list provided to this parameter remains unmodified.</t>
+          <t>- `items`: `List[int]` - The list of integers to be shuffled. This list will not be modified.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>This function provides a non-destructive way to shuffle a list. It operates in two main steps: 1. **Create a Copy:** It first creates a shallow copy of the input `items` list. This step is crucial as it ensures that the original list passed by the user is not altered. 2. **Shuffle the Copy:** It then shuffles the elements of this newly created copy in-place, randomizing their order. A common implementation would use an algorithm like the Fisher-Yates shuffle. Finally, the function returns the...</t>
+          <t>This function provides a safe way to shuffle a list by operating on a copy rather than modifying the original list in place. The process is as follows: 1. The function accepts a list of integers, `items`, as its input. 2. It first creates a shallow copy of the `items` list. This is a crucial step to ensure that the original list passed by the caller remains unchanged. 3. Next, it applies an in-place shuffling algorithm (such as the Fisher-Yates shuffle) to the newly created copy, randomly reo...</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>- The primary feature of this function is that it is **non-destructive**. The original list you pass as an argument will not be changed. - The function returns a **new list**. You must assign the result to a variable to access the shuffled sequence. - Due to the nature of randomization, calling the function multiple times with the identical input list will likely produce different output lists each time. - Although the type hint specifies `List[int]`, the underlying logic works for lists cont...</t>
+          <t>- The original list passed as the `items` argument is not altered. This function is non-destructive. - The returned list will have the exact same elements and length as the input list, only in a different, random order. - Because the shuffling is random, successive calls to `shuffle_copy` with the same input list will likely produce different output lists.</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -526,22 +526,22 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `num` function calculates and returns the sum of two provided arguments.</t>
+          <t>The `num` function returns the sum of two arguments, `a` and `b`.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Description | The first number to be added. | The second number to be added. |</t>
+          <t>Description | The first operand. | The second operand. |</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to perform addition. It accepts two parameters, `a` and `b`, which are expected to be numerical values (integers or floating-point numbers). The core logic of the function uses the `+` operator to compute the sum of `a` and `b`. The resulting value is then returned to the caller. For example, if `a` is `10` and `b` is `5`, the function will compute `10 + 5` and return `15`.</t>
+          <t>This function takes two parameters, `a` and `b`, and applies the addition operator (`+`) to them. The core logic is simply to compute and return the result of `a + b`. The behavior of the function depends on the data types of the input arguments. If both are numbers (integers or floats), it performs mathematical addition. If both are strings, it performs string concatenation.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Important points to consider when using this function: - The function relies on Python's `+` operator. Ensure that both input arguments are of types that support addition (e.g., `int`, `float`). Passing incompatible types (like an `int` and a `NoneType`) will result in a `TypeError`. - If strings are passed as arguments, the function will perform string concatenation instead of mathematical addition. For example, `num("hello", "world")` would return `"helloworld"`. - The data type of the retu...</t>
+          <t>- When `a` and `b` are both numbers (e.g., `int` or `float`), the function returns their mathematical sum. - If `a` and `b` are both strings, the function concatenates them and returns the resulting string. - Passing arguments of incompatible types (e.g., an `int` and a `str`) will result in a `TypeError`. **Output Example**: A numeric value representing the sum.</t>
         </is>
       </c>
     </row>
@@ -556,27 +556,27 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>generate_random_integers</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `num` function is a placeholder that accepts two arguments but performs no operations and returns `None`.</t>
+          <t>The `generate_random_integers` function creates and returns a list of a specified number of pseudo-random integers within a given inclusive range.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Description | The first input parameter. It is not used within the function's body. | The second input parameter. It is not used within the function's body. |</t>
+          <t>Description | The total number of random integers to generate in the list. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>The `num` function is defined with two parameters, `a` and `b`. The function body is currently empty, meaning it contains no logic or operations. Consequently, the function does not utilize the input parameters for any computation. In Python, a function that does not have an explicit `return` statement will implicitly return the `None` object.</t>
+          <t>This function provides a convenient way to generate multiple random integers. It operates in three main steps: 1. **Input Validation**: It first validates the `count` parameter. If `count` is a negative number, the function raises a `ValueError` because it's impossible to generate a negative quantity of numbers. 2. **Range Correction**: The function checks if the `start` value is greater than the `end` value. If this condition is true, it automatically swaps the two values. This ensures that ...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- This function currently acts as a stub or placeholder and lacks any functional implementation. - Calling this function with any arguments will always result in a return value of `None`. - It is likely intended for future development where functionality will be added.</t>
+          <t>- This function depends on Python's built-in `random` module. Ensure it is imported before use. - A `ValueError` will be raised if the `count` argument is less than 0. - The range defined by `start` and `end` is inclusive, meaning both `start` and `end` can appear in the output list. - If `start` is provided as a larger number than `end`, the function will automatically swap them and proceed without error. **Output Example**: A list containing integers.</t>
         </is>
       </c>
     </row>
@@ -591,27 +591,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>generate_random_integers</t>
+          <t>fibonacci</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>The `generate_random_integers` function generates a list of a specified number of pseudo-random integers within a given inclusive range.</t>
+          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an iterative approach.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Description | The number of random integers to generate. This value must be non-negative. | The inclusive lower bound of the random number range. Defaults to `0`. | The inclusive upper bound of the random number range. Defaults to `100`. |</t>
+          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function provides a convenient way to generate a list of pseudo-random integers. It operates in a few distinct steps: 1. **Input Validation**: The function first checks if the `count` parameter is a negative number. If it is, a `ValueError` is raised, as it's impossible to generate a negative quantity of numbers. 2. **Range Correction**: It then verifies if the `start` value is greater than the `end` value. If this condition is true, the function automatically swaps the two values. This ...</t>
+          <t>This function calculates a Fibonacci number based on its index `n`. The Fibonacci sequence is a series of numbers where each number is the sum of the two preceding ones, typically starting with 0 and 1. The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError` because the Fibonacci sequence is not defined for negative indices. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequen...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- The function requires the `random` module to be imported. - A `ValueError` will be raised if a negative value is passed for the `count` parameter. - The range defined by `start` and `end` is inclusive, meaning both `start` and `end` are potential values in the output list. - If `start` is greater than `end`, the function will automatically swap them and proceed without error. **Output Example**: A list of integers. The actual numbers will vary with each execution due to their random nature.</t>
+          <t>- The input `n` must be a non-negative integer. The function will raise a `ValueError` if a negative integer is provided. - The function is 0-indexed. For example, `fibonacci(0)` returns the first number in the sequence, `0`. - This iterative implementation is efficient in terms of memory usage, avoiding the deep recursion stack that can occur with a naive recursive solution, making it suitable for calculating larger Fibonacci numbers. **Output Example**: An integer representing the calculate...</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>generate_random_integers</t>
+          <t>choose_random_item</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The `generate_random_integers` function generates a list containing a specified number of random integers within a given inclusive range.</t>
+          <t>The `choose_random_item` function selects and returns a single, uniformly random element from a given list of strings.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Description | The total number of random integers to generate. This is a required argument. | The inclusive lower bound of the random number range. Defaults to `0`. | The inclusive upper bound of the random number range. Defaults to `100`. |</t>
+          <t>- **items** (`List[str]`): A non-empty list of strings from which a random item will be chosen.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>This function produces a list of pseudo-random integers. The quantity of integers in the resulting list is determined by the `count` parameter. Each integer in the list is generated within the numerical range defined by the `start` and `end` parameters. This range is inclusive, meaning that the values of `start` and `end` themselves are potential outcomes. If the `start` and `end` parameters are not explicitly provided, the function uses a default range from `0` to `100`. The core logic invol...</t>
+          <t>This function provides a simple way to get a random item from a list. The core logic is built around Python's built-in `random` module. First, the function performs a crucial validation check using `if not items:`. It verifies if the provided `items` list is empty. If the list is empty, it is impossible to choose an item, so the function raises a `ValueError` with the message "items must not be empty" to prevent further errors. If the list is not empty, the function proceeds to call `random.c...</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- The value for `start` must be less than or equal to the value for `end`. If `start` is greater than `end`, the underlying random number generation will raise a `ValueError`. - The `count` parameter should be a non-negative integer. If `count` is `0`, an empty list will be returned. - The numbers generated are pseudo-random and should not be used for cryptographic purposes. For security-sensitive applications, consider using the `secrets` module.</t>
+          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function requires the `random` module to be imported in the script where it is used. - The selection is uniformly random, meaning each item in the list has an equal probability of being chosen. **Output Example**: A single string from the input list. For an input of `['red', 'green', 'blue']`, a possible return value is `'green'`.</t>
         </is>
       </c>
     </row>
@@ -661,202 +661,27 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>fibonacci</t>
+          <t>shuffle_copy</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an iterative approach.</t>
+          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original input list remains unchanged.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>- `n`: `int` - The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
+          <t>- **`items`** `List[int]`: A list of integers that will be copied and then shuffled.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>This function calculates a Fibonacci number based on its index `n`. The logic begins by validating the input. If `n` is a negative number, a `ValueError` is raised, as the Fibonacci sequence is not defined for negative indices. The function initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the Fibonacci sequence (F₀ and F₁). It then enters a `for` loop that iterates `n` times. In each iteration, the values of `a` and `b` are updated ...</t>
+          <t>This function provides a safe way to shuffle a list without altering the original data structure, a concept known as non-mutation. The process is straightforward: 1. A shallow copy of the input `items` list is created using `list(items)`. This new list is stored in a local variable named `copy`. 2. The `random.shuffle()` method is then called on the `copy`. This method shuffles the elements of the list in-place, rearranging them into a random order. 3. Finally, the function returns the modifi...</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>- The input `n` must be a non-negative integer. Providing a negative value will result in a `ValueError`. - The function uses a 0-indexed sequence. For example, `fibonacci(0)` returns the first number (`0`), and `fibonacci(1)` returns the second number (`1`). - This iterative implementation is memory-efficient and avoids the recursion depth issues that can occur with naive recursive solutions for large values of `n`. **Output Example**: A possible return value for a valid input.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>fibonacci</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>The `fibonacci` function calculates the n-th number in the Fibonacci sequence.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>- `n` (int): A non-negative integer representing the position (index) in the Fibonacci sequence. The sequence is 0-indexed.</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>This function computes a number in the Fibonacci sequence, which is a series of numbers where each number is the sum of the two preceding ones. The sequence implemented by this function starts with 0 and 1. The function handles the base cases first: - If `n` is 0 or a negative number, it returns 0. - If `n` is 1, it returns 1. For any `n` greater than 1, the function iteratively calculates the value. It initializes two variables, `a` and `b`, to the first two numbers of the sequence (0 and 1)...</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>- The input `n` must be an integer. The function is designed for non-negative integers. - If a negative integer is provided for `n`, the function will return 0. - Be aware that Fibonacci numbers grow exponentially. While Python's integers can handle arbitrary size, calculations for extremely large values of `n` can be computationally intensive and result in very large numbers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>choose_random_item</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>The `choose_random_item` function selects and returns a single, uniformly random item from a given list of strings.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>* **items** (`List[str]`): A non-empty list of strings from which to choose a random item.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a simple way to get a random element from a list. The logic proceeds in two main steps: 1. **Validation**: The function first checks if the provided `items` list is empty using the condition `if not items:`. This is a crucial safeguard to ensure the function operates correctly. If the list is empty, it raises a `ValueError` with the message "items must not be empty", preventing the program from proceeding with invalid input. 2. **Random Selection**: If the list is not e...</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Important points to consider when using this function: - The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's `random` module. Ensure it is imported in the scope where this function is defined or called. - The selection is uniformly random, meaning every item in the list has an equal probability of being chosen. **Output Example**: The function returns a single string. If the input is `['apple', 'banana', 'cherry'...</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>choose_random_item</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>The `choose_random_item` function selects and returns a single, randomly chosen element from a given list of strings.</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>- `items` (`List[str]`): A list of strings from which one item will be randomly selected.</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>This function is designed to perform a random selection from a collection of items. It accepts a single argument, `items`, which is a list of strings. The intended logic is to use a random selection mechanism to pick one of the strings from this list. The standard Python approach for this task is to use the `random.choice()` function from the built-in `random` module. This method takes a non-empty sequence (like a list) and returns a randomly selected element. A complete implementation would ...</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will cause a `random.choice()` call to raise an `IndexError`. - The selection is pseudo-random, meaning the sequence of chosen items is determined by the initial seed of the random number generator. - While the type hint specifies `List[str]`, the underlying `random.choice()` function works with any non-empty sequence (e.g., list of integers, tuples, etc.).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>shuffle_copy</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function returns a shuffled copy of a given list of integers without modifying the original list.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>- `items` (List[int]): A list of integers to be copied and shuffled.</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to shuffle a list by operating on a copy rather than the original data. The process is as follows: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This step is crucial as it ensures that the original list passed to the function remains unchanged. 2. The `random.shuffle()` method is then called on the `copy`. This function shuffles the elements of the `copy` list in-place, rearranging them into a random order. 3. Finally, the...</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>- This function is non-mutating, meaning the original list you pass as an argument will not be altered. - The function depends on Python's built-in `random` module. Ensure this module is available in the environment. - The order of the elements in the returned list is non-deterministic and will be different on each execution. **Output Example**: A new list containing the same integers as the input list, but in a random order. For an input of `[1, 2, 3, 4, 5]`, a possible output could be `[3, ...</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>shuffle_copy</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function creates and returns a new list containing the same elements as the input list but arranged in a random order.</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>- `items`: `List[int]` - The list of integers to be shuffled. This list will not be modified.</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to shuffle a list by operating on a copy rather than modifying the original list in place. The process is as follows: 1. The function accepts a list of integers, `items`, as its input. 2. It first creates a shallow copy of the `items` list. This is a crucial step to ensure that the original list passed by the caller remains unchanged. 3. Next, it applies an in-place shuffling algorithm (such as the Fisher-Yates shuffle) to the newly created copy, randomly reo...</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>- The original list passed as the `items` argument is not altered. This function is non-destructive. - The returned list will have the exact same elements and length as the input list, only in a different, random order. - Because the shuffling is random, successive calls to `shuffle_copy` with the same input list will likely produce different output lists.</t>
+          <t>- This function is non-mutating, meaning the original list passed as the `items` parameter will not be modified. - The function depends on Python's built-in `random` module. You must ensure `import random` is present in your script for `random.shuffle()` to be accessible. - The returned list will always contain the exact same elements and have the same length as the input list; only their order is changed. **Output Example**: A new list with the same elements as the input list, but in a rando...</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -526,22 +526,22 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `num` function returns the sum of two arguments, `a` and `b`.</t>
+          <t>The `num` function calculates and returns the sum of two input numbers.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Description | The first operand. | The second operand. |</t>
+          <t>Description | The first number to be added. | The second number to be added. |</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function takes two parameters, `a` and `b`, and applies the addition operator (`+`) to them. The core logic is simply to compute and return the result of `a + b`. The behavior of the function depends on the data types of the input arguments. If both are numbers (integers or floats), it performs mathematical addition. If both are strings, it performs string concatenation.</t>
+          <t>The `num` function provides a straightforward implementation of addition. It accepts two arguments, `a` and `b`, which are expected to be numeric. The function uses the standard Python addition operator (`+`) to compute the sum of these two arguments. The resulting value is then immediately returned to the caller.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- When `a` and `b` are both numbers (e.g., `int` or `float`), the function returns their mathematical sum. - If `a` and `b` are both strings, the function concatenates them and returns the resulting string. - Passing arguments of incompatible types (e.g., an `int` and a `str`) will result in a `TypeError`. **Output Example**: A numeric value representing the sum.</t>
+          <t>- This function is primarily intended for use with numeric types such as integers (`int`) and floating-point numbers (`float`). - If strings are passed as arguments, the function will perform string concatenation instead of mathematical addition. For example, `num("hello", " world")` would return `"hello world"`. - Providing incompatible types (e.g., an `int` and a `str`) will result in a `TypeError`. **Output Example**: A numeric value representing the sum. For `num(5, 10)`, the output is `15`.</t>
         </is>
       </c>
     </row>
@@ -566,17 +566,17 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Description | The total number of random integers to generate in the list. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
+          <t>Description | The number of integers to generate. This value must be non-negative. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a convenient way to generate multiple random integers. It operates in three main steps: 1. **Input Validation**: It first validates the `count` parameter. If `count` is a negative number, the function raises a `ValueError` because it's impossible to generate a negative quantity of numbers. 2. **Range Correction**: The function checks if the `start` value is greater than the `end` value. If this condition is true, it automatically swaps the two values. This ensures that ...</t>
+          <t>This function provides a robust way to generate a list of random integers. Its logic proceeds in three main steps: 1. **Input Validation**: The function first validates the `count` parameter. If `count` is a negative number, it is impossible to generate a list of that size, so the function raises a `ValueError` with the message "count must be non-negative". 2. **Range Correction**: It then checks if the provided `start` value is greater than the `end` value. If this is the case, the function ...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- This function depends on Python's built-in `random` module. Ensure it is imported before use. - A `ValueError` will be raised if the `count` argument is less than 0. - The range defined by `start` and `end` is inclusive, meaning both `start` and `end` can appear in the output list. - If `start` is provided as a larger number than `end`, the function will automatically swap them and proceed without error. **Output Example**: A list containing integers.</t>
+          <t>- The function will raise a `ValueError` if the `count` argument is a negative integer. - If `start` is greater than `end`, the function will automatically swap them to create a valid range; no error will be raised. - The range defined by `start` and `end` is inclusive, meaning both `start` and `end` can appear in the output list. - This function requires the `random` module to be imported in the script. **Output Example**: A possible return value for `generate_random_integers(5, 1, 100)`:</t>
         </is>
       </c>
     </row>
@@ -601,17 +601,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
+          <t>- `n`: `int` - The 0-indexed position in the Fibonacci sequence for which to find the corresponding number.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function calculates a Fibonacci number based on its index `n`. The Fibonacci sequence is a series of numbers where each number is the sum of the two preceding ones, typically starting with 0 and 1. The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError` because the Fibonacci sequence is not defined for negative indices. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequen...</t>
+          <t>This function provides a memory-efficient, iterative method to calculate a number in the Fibonacci sequence. The Fibonacci sequence is a series of numbers where each number is the sum of the two preceding ones, starting from 0 and 1. The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError`, as the Fibonacci sequence is not defined for negative indices. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the firs...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- The input `n` must be a non-negative integer. The function will raise a `ValueError` if a negative integer is provided. - The function is 0-indexed. For example, `fibonacci(0)` returns the first number in the sequence, `0`. - This iterative implementation is efficient in terms of memory usage, avoiding the deep recursion stack that can occur with a naive recursive solution, making it suitable for calculating larger Fibonacci numbers. **Output Example**: An integer representing the calculate...</t>
+          <t>- The index `n` is 0-based. For example, `fibonacci(0)` returns `0` and `fibonacci(1)` returns `1`. - The function will raise a `ValueError` if a negative integer is provided as an argument. - This iterative implementation is preferred over simple recursion for larger values of `n` as it avoids deep recursion stacks and redundant calculations, resulting in better performance and memory usage. **Output Example**:</t>
         </is>
       </c>
     </row>
@@ -631,22 +631,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single, uniformly random element from a given list of strings.</t>
+          <t>The `choose_random_item` function chooses a single random item from a non-empty list of strings.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>- **items** (`List[str]`): A non-empty list of strings from which a random item will be chosen.</t>
+          <t>- `items` (`List[str]`): A list of strings from which one item will be randomly selected.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>This function provides a simple way to get a random item from a list. The core logic is built around Python's built-in `random` module. First, the function performs a crucial validation check using `if not items:`. It verifies if the provided `items` list is empty. If the list is empty, it is impossible to choose an item, so the function raises a `ValueError` with the message "items must not be empty" to prevent further errors. If the list is not empty, the function proceeds to call `random.c...</t>
+          <t>This function provides a straightforward way to select one item at random from a given list. The function begins by checking if the input list `items` is empty. If it is, the function raises a `ValueError` with the message "items must not be empty" to prevent further execution with invalid input. If the list contains one or more items, the function utilizes the `random.choice()` method. This method, part of Python's standard `random` module, performs a uniform random selection from the sequen...</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function requires the `random` module to be imported in the script where it is used. - The selection is uniformly random, meaning each item in the list has an equal probability of being chosen. **Output Example**: A single string from the input list. For an input of `['red', 'green', 'blue']`, a possible return value is `'green'`.</t>
+          <t>- The input list `items` must not be empty. Providing an empty list will raise a `ValueError`. - This function depends on Python's `random` module, which must be imported into the environment where the function is used. - The selection is uniformly random, ensuring each item in the list has an equal chance of being returned. **Output Example**: The function returns a single string from the input list. For an input of `["apple", "banana", "cherry"]`, a possible return value is `"banana"`.</t>
         </is>
       </c>
     </row>
@@ -666,22 +666,22 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list, ensuring the original input list remains unchanged.</t>
+          <t>The `shuffle_copy` function returns a shuffled copy of a given list without modifying the original list.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>- **`items`** `List[int]`: A list of integers that will be copied and then shuffled.</t>
+          <t>- `items`: (Type: `List[int]`) A list of integers to be shuffled.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to shuffle a list without altering the original data structure, a concept known as non-mutation. The process is straightforward: 1. A shallow copy of the input `items` list is created using `list(items)`. This new list is stored in a local variable named `copy`. 2. The `random.shuffle()` method is then called on the `copy`. This method shuffles the elements of the list in-place, rearranging them into a random order. 3. Finally, the function returns the modifi...</t>
+          <t>This function provides a safe way to shuffle a list by ensuring the original data structure is not altered. The process is executed in three main steps: 1. A shallow copy of the input `items` list is created using the `list()` constructor. This new list is assigned to a local variable `copy`. This is the key step that prevents mutation of the original list. 2. The `random.shuffle()` function is then called on the `copy`. This function shuffles the elements of the `copy` list in-place, rearran...</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>- This function is non-mutating, meaning the original list passed as the `items` parameter will not be modified. - The function depends on Python's built-in `random` module. You must ensure `import random` is present in your script for `random.shuffle()` to be accessible. - The returned list will always contain the exact same elements and have the same length as the input list; only their order is changed. **Output Example**: A new list with the same elements as the input list, but in a rando...</t>
+          <t>- This function is non-mutating, meaning the original list passed as the `items` parameter will remain unchanged after the function call. - The function depends on Python's standard `random` module. Ensure you have `import random` at the beginning of your script to use it. - The randomness is based on the default random number generator in the `random` module. **Output Example**: The function returns a new list. For an input of `[1, 2, 3, 4]`, a possible output could be:</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -526,22 +526,22 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `num` function calculates and returns the sum of two input numbers.</t>
+          <t>The `num` function returns the result of applying the addition operator (`+`) to two input arguments.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Description | The first number to be added. | The second number to be added. |</t>
+          <t>Description | The first operand for the addition or concatenation operation. | The second operand, which must be type-compatible with `a` for the `+` operator. |</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>The `num` function provides a straightforward implementation of addition. It accepts two arguments, `a` and `b`, which are expected to be numeric. The function uses the standard Python addition operator (`+`) to compute the sum of these two arguments. The resulting value is then immediately returned to the caller.</t>
+          <t>This function takes two parameters, `a` and `b`, and returns the result of the expression `a + b`. The behavior of the function is dependent on the data types of the provided arguments. If the arguments `a` and `b` are numeric (such as `int` or `float`), the function will perform arithmetic addition and return their sum. If the arguments are of a sequence type like a string (`str`), the function will perform concatenation.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- This function is primarily intended for use with numeric types such as integers (`int`) and floating-point numbers (`float`). - If strings are passed as arguments, the function will perform string concatenation instead of mathematical addition. For example, `num("hello", " world")` would return `"hello world"`. - Providing incompatible types (e.g., an `int` and a `str`) will result in a `TypeError`. **Output Example**: A numeric value representing the sum. For `num(5, 10)`, the output is `15`.</t>
+          <t>- This function will raise a `TypeError` if the operands `a` and `b` are of incompatible types for the `+` operator (e.g., attempting to add an `int` to a `str`). - The caller is responsible for ensuring that the arguments are of compatible types, as the function does not perform any internal type checking or conversion. **Output Example**: A numeric return value from adding two integers.</t>
         </is>
       </c>
     </row>
@@ -561,22 +561,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `generate_random_integers` function creates and returns a list of a specified number of pseudo-random integers within a given inclusive range.</t>
+          <t>The `generate_random_integers` function returns a list of a specified number of pseudo-random integers within a given inclusive range.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Description | The number of integers to generate. This value must be non-negative. | The inclusive lower bound for the random values. Defaults to `0`. | The inclusive upper bound for the random values. Defaults to `100`. |</t>
+          <t>Description | The number of random integers to generate. This value must be non-negative. | The inclusive lower bound for the random integer values. Defaults to `0`. | The inclusive upper bound for the random integer values. Defaults to `100`. |</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a robust way to generate a list of random integers. Its logic proceeds in three main steps: 1. **Input Validation**: The function first validates the `count` parameter. If `count` is a negative number, it is impossible to generate a list of that size, so the function raises a `ValueError` with the message "count must be non-negative". 2. **Range Correction**: It then checks if the provided `start` value is greater than the `end` value. If this is the case, the function ...</t>
+          <t>This function provides a robust way to generate a list of random integers. The process begins with input validation. First, it checks if the `count` parameter is a negative number. If `count` is less than zero, the function raises a `ValueError` to prevent invalid list creation. Next, it ensures the range is valid by comparing `start` and `end`. If `start` is found to be greater than `end`, the function automatically swaps their values. This convenience feature allows the user to provide the ...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- The function will raise a `ValueError` if the `count` argument is a negative integer. - If `start` is greater than `end`, the function will automatically swap them to create a valid range; no error will be raised. - The range defined by `start` and `end` is inclusive, meaning both `start` and `end` can appear in the output list. - This function requires the `random` module to be imported in the script. **Output Example**: A possible return value for `generate_random_integers(5, 1, 100)`:</t>
+          <t>- This function requires the `random` module to be imported to work correctly. - A `ValueError` will be raised if the `count` argument is a negative integer. - The function gracefully handles cases where `start &gt; end` by swapping the values, so the order of range bounds does not matter. - The generated integers are sampled uniformly from the range, inclusive of both `start` and `end`. **Output Example**: A possible return value for `generate_random_integers(5, 1, 100)`:</t>
         </is>
       </c>
     </row>
@@ -601,17 +601,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `n`: `int` - The 0-indexed position in the Fibonacci sequence for which to find the corresponding number.</t>
+          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function provides a memory-efficient, iterative method to calculate a number in the Fibonacci sequence. The Fibonacci sequence is a series of numbers where each number is the sum of the two preceding ones, starting from 0 and 1. The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError`, as the Fibonacci sequence is not defined for negative indices. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the firs...</t>
+          <t>This function calculates a Fibonacci number based on its index `n`. The logic begins by validating the input. If `n` is a negative number, a `ValueError` is raised, as the Fibonacci sequence is not defined for negative indices. The function initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the Fibonacci sequence, F(0) and F(1). It then enters a `for` loop that iterates `n` times. In each iteration, the values of `a` and `b` are updat...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- The index `n` is 0-based. For example, `fibonacci(0)` returns `0` and `fibonacci(1)` returns `1`. - The function will raise a `ValueError` if a negative integer is provided as an argument. - This iterative implementation is preferred over simple recursion for larger values of `n` as it avoids deep recursion stacks and redundant calculations, resulting in better performance and memory usage. **Output Example**:</t>
+          <t>- The input `n` must be a non-negative integer. Providing a negative value will result in a `ValueError`. - The function uses a 0-indexed sequence, meaning `fibonacci(0)` returns the first number of the sequence, which is `0`. - This iterative implementation is efficient in terms of memory, as it avoids the deep recursion stacks that can occur with naive recursive solutions, making it suitable for calculating larger Fibonacci numbers. **Output Example**: A single integer representing the calc...</t>
         </is>
       </c>
     </row>
@@ -631,22 +631,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function chooses a single random item from a non-empty list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single, uniformly random item from a given list of strings.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>- `items` (`List[str]`): A list of strings from which one item will be randomly selected.</t>
+          <t>- **`items`** `List[str]`: A non-empty list of strings from which a random item will be chosen.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to select one item at random from a given list. The function begins by checking if the input list `items` is empty. If it is, the function raises a `ValueError` with the message "items must not be empty" to prevent further execution with invalid input. If the list contains one or more items, the function utilizes the `random.choice()` method. This method, part of Python's standard `random` module, performs a uniform random selection from the sequen...</t>
+          <t>This function provides a simple way to randomly select one element from a sequence. The core logic is implemented in two steps: 1. **Validation**: The function first checks if the provided `items` list is empty using `if not items:`. If the list is empty, it is impossible to choose an item, so the function raises a `ValueError` with the message `"items must not be empty"`. This prevents runtime errors from the underlying `random.choice` method, which cannot handle empty sequences. 2. **Select...</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will raise a `ValueError`. - This function depends on Python's `random` module, which must be imported into the environment where the function is used. - The selection is uniformly random, ensuring each item in the list has an equal chance of being returned. **Output Example**: The function returns a single string from the input list. For an input of `["apple", "banana", "cherry"]`, a possible return value is `"banana"`.</t>
+          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's `random` module. Ensure that `import random` is present at the top of the script where this function is defined or used. - The selection is uniformly random, meaning each item in the list has an equal probability of being chosen. **Output Example**: The function returns a single string from the input list. For an input of `["apple", "banana", "cherry"]`, a pos...</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>- `items`: (Type: `List[int]`) A list of integers to be shuffled.</t>
+          <t>- `items`: `List[int]` - A list of integers that you want to shuffle.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to shuffle a list by ensuring the original data structure is not altered. The process is executed in three main steps: 1. A shallow copy of the input `items` list is created using the `list()` constructor. This new list is assigned to a local variable `copy`. This is the key step that prevents mutation of the original list. 2. The `random.shuffle()` function is then called on the `copy`. This function shuffles the elements of the `copy` list in-place, rearran...</t>
+          <t>This function provides a safe way to shuffle a list by operating on a copy rather than the original data. The process is as follows: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This step is crucial as it ensures that the original list passed to the function remains unchanged. 2. The `random.shuffle()` function is then called on this `copy`. `random.shuffle()` shuffles the elements of the list in-place, rearranging them into a random order. 3. Finally, th...</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>- This function is non-mutating, meaning the original list passed as the `items` parameter will remain unchanged after the function call. - The function depends on Python's standard `random` module. Ensure you have `import random` at the beginning of your script to use it. - The randomness is based on the default random number generator in the `random` module. **Output Example**: The function returns a new list. For an input of `[1, 2, 3, 4]`, a possible output could be:</t>
+          <t>- **Non-mutating**: The primary benefit of this function is that it does not mutate (change) the input list. The original list remains in its initial order after the function call. - **Shallow Copy**: The function creates a shallow copy. For a list of integers, this is sufficient. If the list contained mutable objects (like other lists or dictionaries), changes to those nested objects would be reflected in both the original and the copied list. - **Randomness**: The shuffling is pseudo-random...</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -526,22 +526,22 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `num` function returns the result of applying the addition operator (`+`) to two input arguments.</t>
+          <t>The `num` function calculates and returns the sum of two numbers.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Description | The first operand for the addition or concatenation operation. | The second operand, which must be type-compatible with `a` for the `+` operator. |</t>
+          <t>Description | The first number to be added. | The second number to be added. |</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function takes two parameters, `a` and `b`, and returns the result of the expression `a + b`. The behavior of the function is dependent on the data types of the provided arguments. If the arguments `a` and `b` are numeric (such as `int` or `float`), the function will perform arithmetic addition and return their sum. If the arguments are of a sequence type like a string (`str`), the function will perform concatenation.</t>
+          <t>This function provides a straightforward way to perform addition. It accepts two arguments, `a` and `b`, and executes the addition operation `a + b`. The resulting sum is then returned by the function. The function is designed to work with numeric types, including both integers and floating-point numbers.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- This function will raise a `TypeError` if the operands `a` and `b` are of incompatible types for the `+` operator (e.g., attempting to add an `int` to a `str`). - The caller is responsible for ensuring that the arguments are of compatible types, as the function does not perform any internal type checking or conversion. **Output Example**: A numeric return value from adding two integers.</t>
+          <t>- Ensure that both parameters are numeric types (e.g., `int`, `float`) to perform a mathematical sum. - If string types are provided for both `a` and `b`, the function will perform string concatenation instead of numerical addition. - Providing incompatible types (e.g., an `int` and a `str`) will raise a `TypeError`. **Output Example**: A single numeric value representing the sum. For instance, if `a` is `10` and `b` is `5`, the output will be `15`.</t>
         </is>
       </c>
     </row>
@@ -561,22 +561,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `generate_random_integers` function returns a list of a specified number of pseudo-random integers within a given inclusive range.</t>
+          <t>The `generate_random_integers` function generates a list of a specified number of pseudo-random integers within a given inclusive range.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Description | The number of random integers to generate. This value must be non-negative. | The inclusive lower bound for the random integer values. Defaults to `0`. | The inclusive upper bound for the random integer values. Defaults to `100`. |</t>
+          <t>Description | The number of random integers to generate. This value must be non-negative. | The inclusive lower bound for the generated values. Defaults to `0`. | The inclusive upper bound for the generated values. Defaults to `100`. |</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a robust way to generate a list of random integers. The process begins with input validation. First, it checks if the `count` parameter is a negative number. If `count` is less than zero, the function raises a `ValueError` to prevent invalid list creation. Next, it ensures the range is valid by comparing `start` and `end`. If `start` is found to be greater than `end`, the function automatically swaps their values. This convenience feature allows the user to provide the ...</t>
+          <t>This function provides a convenient way to create a list of pseudo-random integers. It operates in three main steps: 1. **Input Validation**: The function first checks if the `count` parameter is less than zero. If it is, a `ValueError` is raised, as it's not possible to generate a negative number of integers. 2. **Range Correction**: It then compares the `start` and `end` parameters. If `start` is found to be greater than `end`, the function automatically swaps their values. This ensures tha...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- This function requires the `random` module to be imported to work correctly. - A `ValueError` will be raised if the `count` argument is a negative integer. - The function gracefully handles cases where `start &gt; end` by swapping the values, so the order of range bounds does not matter. - The generated integers are sampled uniformly from the range, inclusive of both `start` and `end`. **Output Example**: A possible return value for `generate_random_integers(5, 1, 100)`:</t>
+          <t>- The function requires the `random` module to be imported to work correctly. - A `ValueError` will be raised if the `count` argument is a negative number. - The range defined by `start` and `end` is inclusive, meaning both boundary values can be included in the results. - If the provided `start` value is greater than the `end` value, the function will automatically swap them to form a valid range. **Output Example**: The function returns a list of integers. For a call with `count=5`, `start=...</t>
         </is>
       </c>
     </row>
@@ -601,17 +601,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
+          <t>- `n`: `int` | The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function calculates a Fibonacci number based on its index `n`. The logic begins by validating the input. If `n` is a negative number, a `ValueError` is raised, as the Fibonacci sequence is not defined for negative indices. The function initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the Fibonacci sequence, F(0) and F(1). It then enters a `for` loop that iterates `n` times. In each iteration, the values of `a` and `b` are updat...</t>
+          <t>This function calculates a Fibonacci number based on its index `n`. It employs an iterative method for efficiency and to avoid recursion depth limits. The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError` as the Fibonacci sequence is not defined for negative indices. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequence, F(0) and F(1). The core logic resides in a `for` loop...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- The input `n` must be a non-negative integer. Providing a negative value will result in a `ValueError`. - The function uses a 0-indexed sequence, meaning `fibonacci(0)` returns the first number of the sequence, which is `0`. - This iterative implementation is efficient in terms of memory, as it avoids the deep recursion stacks that can occur with naive recursive solutions, making it suitable for calculating larger Fibonacci numbers. **Output Example**: A single integer representing the calc...</t>
+          <t>- The index `n` is 0-indexed. For example, `fibonacci(0)` returns `0`, and `fibonacci(1)` returns `1`. - The function will raise a `ValueError` if a negative integer is provided for `n`. - This iterative implementation is memory-efficient and is preferred over simple recursive solutions for large values of `n` to prevent stack overflow errors. **Output Example**: The function returns a single integer representing the Fibonacci number at the specified index.</t>
         </is>
       </c>
     </row>
@@ -631,22 +631,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single, uniformly random item from a given list of strings.</t>
+          <t>The `choose_random_item` function selects and returns a single random string from a given list of strings.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>- **`items`** `List[str]`: A non-empty list of strings from which a random item will be chosen.</t>
+          <t>- `items`: `List[str]` - A non-empty list of strings from which a single item will be chosen randomly.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>This function provides a simple way to randomly select one element from a sequence. The core logic is implemented in two steps: 1. **Validation**: The function first checks if the provided `items` list is empty using `if not items:`. If the list is empty, it is impossible to choose an item, so the function raises a `ValueError` with the message `"items must not be empty"`. This prevents runtime errors from the underlying `random.choice` method, which cannot handle empty sequences. 2. **Select...</t>
+          <t>This function provides a simple way to get a random element from a sequence of strings. The core logic is built around Python's `random.choice()` method. Before attempting to select an item, the function first performs a validation check to ensure the input list `items` is not empty. If the list is empty (`if not items`), the function raises a `ValueError` with the message "items must not be empty" to prevent runtime errors from `random.choice()`, which cannot operate on an empty sequence. If...</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will result in a `ValueError`. - This function depends on Python's `random` module. Ensure that `import random` is present at the top of the script where this function is defined or used. - The selection is uniformly random, meaning each item in the list has an equal probability of being chosen. **Output Example**: The function returns a single string from the input list. For an input of `["apple", "banana", "cherry"]`, a pos...</t>
+          <t>- The input list `items` must not be empty. Providing an empty list will raise a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in the environment where the function is defined. - The selection is uniformly random, meaning each item in the list has an equal probability of being chosen on any given call. **Output Example**: The function returns a single string from the input list.</t>
         </is>
       </c>
     </row>
@@ -666,22 +666,22 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>The `shuffle_copy` function returns a shuffled copy of a given list without modifying the original list.</t>
+          <t>The `shuffle_copy` function creates and returns a randomly shuffled copy of a list, ensuring the original list remains unchanged.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>- `items`: `List[int]` - A list of integers that you want to shuffle.</t>
+          <t>- `items`: `List[int]` - A list of integers to be shuffled.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>This function provides a safe way to shuffle a list by operating on a copy rather than the original data. The process is as follows: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This step is crucial as it ensures that the original list passed to the function remains unchanged. 2. The `random.shuffle()` function is then called on this `copy`. `random.shuffle()` shuffles the elements of the list in-place, rearranging them into a random order. 3. Finally, th...</t>
+          <t>This function provides a safe way to shuffle a list without modifying the original data structure (a concept known as immutability). The process is straightforward: 1. The function first creates a shallow copy of the input `items` list by calling `list(items)`. This new list is stored in a variable named `copy`. 2. It then uses the `random.shuffle()` method, which shuffles a sequence in-place. By applying this method to the `copy`, only the new list is reordered. 3. Finally, the function retu...</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>- **Non-mutating**: The primary benefit of this function is that it does not mutate (change) the input list. The original list remains in its initial order after the function call. - **Shallow Copy**: The function creates a shallow copy. For a list of integers, this is sufficient. If the list contained mutable objects (like other lists or dictionaries), changes to those nested objects would be reflected in both the original and the copied list. - **Randomness**: The shuffling is pseudo-random...</t>
+          <t>- The primary benefit of this function is that it is non-mutating. The original list passed as the `items` parameter will not be altered. - This function depends on Python's built-in `random` module. Ensure that `random` is imported in your script before calling this function. - The function creates a shallow copy. If the list contains mutable objects (like other lists or dictionaries), the references to those objects are shuffled, but the objects themselves are not duplicated. **Output Examp...</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -526,22 +526,22 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `num` function calculates and returns the sum of two numbers.</t>
+          <t>The `num` function calculates and returns the sum of two provided numbers.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Description | The first number to be added. | The second number to be added. |</t>
+          <t>Description | The first number to be used in the addition. | The second number to be used in the addition. |</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to perform addition. It accepts two arguments, `a` and `b`, and executes the addition operation `a + b`. The resulting sum is then returned by the function. The function is designed to work with numeric types, including both integers and floating-point numbers.</t>
+          <t>This function performs a basic arithmetic addition. It accepts two arguments, `a` and `b`, and computes their sum using the `+` operator. The resulting value is then returned by the function. The function is straightforward and does not contain any complex logic or error handling. For example, if `a` is `5` and `b` is `10`, the function will compute `5 + 10` and return `15`.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- Ensure that both parameters are numeric types (e.g., `int`, `float`) to perform a mathematical sum. - If string types are provided for both `a` and `b`, the function will perform string concatenation instead of numerical addition. - Providing incompatible types (e.g., an `int` and a `str`) will raise a `TypeError`. **Output Example**: A single numeric value representing the sum. For instance, if `a` is `10` and `b` is `5`, the output will be `15`.</t>
+          <t>Important points to consider when using this function: - The function is designed for numeric types like integers (`int`) and floating-point numbers (`float`). - If strings are passed as arguments, the function will perform string concatenation instead of arithmetic addition (e.g., `num("hello", "world")` would return `"helloworld"`). - The order of the parameters `a` and `b` does not affect the result due to the commutative property of addition. **Output Example**: A single numeric value rep...</t>
         </is>
       </c>
     </row>
@@ -561,22 +561,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `generate_random_integers` function generates a list of a specified number of pseudo-random integers within a given inclusive range.</t>
+          <t>The `generate_random_integers` function creates and returns a list of a specified number of pseudo-random integers within a given inclusive range.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Description | The number of random integers to generate. This value must be non-negative. | The inclusive lower bound for the generated values. Defaults to `0`. | The inclusive upper bound for the generated values. Defaults to `100`. |</t>
+          <t>Description | The total number of random integers to generate. This value must be non-negative. | The inclusive lower bound of the random number range. Defaults to `0`. | The inclusive upper bound of the random number range. Defaults to `100`. |</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a convenient way to create a list of pseudo-random integers. It operates in three main steps: 1. **Input Validation**: The function first checks if the `count` parameter is less than zero. If it is, a `ValueError` is raised, as it's not possible to generate a negative number of integers. 2. **Range Correction**: It then compares the `start` and `end` parameters. If `start` is found to be greater than `end`, the function automatically swaps their values. This ensures tha...</t>
+          <t>This function provides a straightforward way to generate a list of random integers. The logic proceeds as follows: 1. **Input Validation**: The function first checks if the `count` parameter is a non-negative number. If `count` is less than zero, it raises a `ValueError` because it's impossible to generate a negative number of integers. 2. **Range Correction**: It then compares the `start` and `end` parameters. If `start` is found to be greater than `end`, the function automatically swaps the...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- The function requires the `random` module to be imported to work correctly. - A `ValueError` will be raised if the `count` argument is a negative number. - The range defined by `start` and `end` is inclusive, meaning both boundary values can be included in the results. - If the provided `start` value is greater than the `end` value, the function will automatically swap them to form a valid range. **Output Example**: The function returns a list of integers. For a call with `count=5`, `start=...</t>
+          <t>- This function depends on Python's `random` module. Ensure it is imported before calling the function. - The function gracefully handles cases where `start &gt; end` by swapping the values internally, so the order of these two parameters does not affect the outcome. - An attempt to generate a negative number of integers (e.g., `count=-1`) will result in a `ValueError`. - The range defined by `start` and `end` is inclusive, meaning both `start` and `end` are potential values in the output list. ...</t>
         </is>
       </c>
     </row>
@@ -591,27 +591,23 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>fibonacci</t>
+          <t>choose_random_item</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an iterative approach.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>- `n`: `int` | The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
-        </is>
-      </c>
+          <t>The `choose_random_item` function selects and returns a single item chosen uniformly at random from a provided list of strings.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function calculates a Fibonacci number based on its index `n`. It employs an iterative method for efficiency and to avoid recursion depth limits. The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError` as the Fibonacci sequence is not defined for negative indices. It initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequence, F(0) and F(1). The core logic resides in a `for` loop...</t>
+          <t>This function provides a safe way to select a random element from a list. It begins by performing a validation check on the input list `items`. If the list is empty (`if not items`), the function immediately raises a `ValueError` to prevent errors that would occur from attempting to choose an item from an empty sequence. If the list is not empty, the function proceeds to use `random.choice(items)`. This is a standard library function from Python's `random` module that takes a non-empty sequen...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- The index `n` is 0-indexed. For example, `fibonacci(0)` returns `0`, and `fibonacci(1)` returns `1`. - The function will raise a `ValueError` if a negative integer is provided for `n`. - This iterative implementation is memory-efficient and is preferred over simple recursive solutions for large values of `n` to prevent stack overflow errors. **Output Example**: The function returns a single integer representing the Fibonacci number at the specified index.</t>
+          <t>* The function requires the `random` module to be imported to work correctly. * Passing an empty list to this function will result in a `ValueError`. Ensure the list contains at least one element before calling. * The function is designed for a `List[str]`, but `random.choice` can work with any non-empty sequence (like tuples or other list types). **Output Example**: A single string from the input list.</t>
         </is>
       </c>
     </row>
@@ -626,27 +622,27 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>choose_random_item</t>
+          <t>shuffle_copy</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The `choose_random_item` function selects and returns a single random string from a given list of strings.</t>
+          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list without modifying the original list.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>- `items`: `List[str]` - A non-empty list of strings from which a single item will be chosen randomly.</t>
+          <t>- `items` (`List[int]`): The list of integers to be shuffled.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>This function provides a simple way to get a random element from a sequence of strings. The core logic is built around Python's `random.choice()` method. Before attempting to select an item, the function first performs a validation check to ensure the input list `items` is not empty. If the list is empty (`if not items`), the function raises a `ValueError` with the message "items must not be empty" to prevent runtime errors from `random.choice()`, which cannot operate on an empty sequence. If...</t>
+          <t>This function provides a safe way to shuffle a list by ensuring the original data structure remains unchanged. The process is straightforward: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is the key step that prevents mutation of the original list. 2. The `random.shuffle()` function is then called on this new `copy`. This function shuffles the elements of the list in-place, rearranging them into a random order. 3. Finally, the shuffled `copy` is retu...</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- The input list `items` must not be empty. Providing an empty list will raise a `ValueError`. - This function depends on Python's built-in `random` module. Ensure it is imported in the environment where the function is defined. - The selection is uniformly random, meaning each item in the list has an equal probability of being chosen on any given call. **Output Example**: The function returns a single string from the input list.</t>
+          <t>- **Non-mutating:** The primary benefit of this function is that it does not alter the original list provided as an argument. This prevents unintended side effects in your code. - **Dependency:** This function relies on Python's built-in `random` module. You must ensure `import random` is present in your script for the function to work. - **Type Flexibility:** While the type hint specifies `List[int]`, the function's logic will work correctly with lists containing other data types, such as st...</t>
         </is>
       </c>
     </row>
@@ -661,27 +657,97 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>fibonacci</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an iterative method.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>This function provides an efficient, iterative way to calculate a Fibonacci number. The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError` because the Fibonacci sequence is not defined for negative indices. It then initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequence, F₀ and F₁. The core logic resides in a `for` loop that iterates `n` times. In each iteration, the values of `a...</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>- The input `n` must be a non-negative integer. Providing a negative integer will result in a `ValueError`. - This function uses an iterative approach, which is memory-efficient and avoids the recursion depth limits that can affect recursive solutions for large values of `n`. - The sequence is 0-indexed, meaning `fibonacci(0)` returns the first number (0), `fibonacci(1)` returns the second (1), and so on. **Output Example**:</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>choose_random_item</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>The `choose_random_item` function selects and returns a single, random element from a provided list of strings.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>- `items` (`List[str]`): A list of strings from which a random item will be selected. This list must not be empty.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>This function provides a straightforward way to get a random element from a sequence. The logic proceeds in two steps: First, it performs a validation check on the input `items` list. The condition `if not items:` evaluates to `True` if the list is empty. In this case, the function raises a `ValueError` to prevent errors in the random selection logic and to enforce the requirement that the input sequence must be non-empty. If the `items` list is not empty, the function uses `random.choice(ite...</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>- The input list `items` cannot be empty. Passing an empty list will result in a `ValueError`. - The function relies on Python's built-in `random` module. Ensure this module is imported and available in the execution environment. - The selection is uniformly random, meaning every string in the `items` list has an equal probability of being returned. **Output Example**: A single string that was present in the input `items` list. For example, `"apple"`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>shuffle_copy</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function creates and returns a randomly shuffled copy of a list, ensuring the original list remains unchanged.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>- `items`: `List[int]` - A list of integers to be shuffled.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to shuffle a list without modifying the original data structure (a concept known as immutability). The process is straightforward: 1. The function first creates a shallow copy of the input `items` list by calling `list(items)`. This new list is stored in a variable named `copy`. 2. It then uses the `random.shuffle()` method, which shuffles a sequence in-place. By applying this method to the `copy`, only the new list is reordered. 3. Finally, the function retu...</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>- The primary benefit of this function is that it is non-mutating. The original list passed as the `items` parameter will not be altered. - This function depends on Python's built-in `random` module. Ensure that `random` is imported in your script before calling this function. - The function creates a shallow copy. If the list contains mutable objects (like other lists or dictionaries), the references to those objects are shuffled, but the objects themselves are not duplicated. **Output Examp...</t>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>The `shuffle_copy` function creates and returns a new list containing the elements of the input list in a randomized order, leaving the original list unchanged.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>- **`items`** (`List[int]`): A list of integers to be copied and shuffled.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>This function provides a safe way to shuffle a list without altering the original data structure. The logic proceeds in three steps: 1. First, a shallow copy of the input `items` list is created using the `list()` constructor. This ensures that any subsequent modifications do not affect the original list provided by the user. 2. Next, the `random.shuffle()` function is called on the newly created `copy`. The `random.shuffle()` method shuffles the elements of a list "in-place," meaning it dire...</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Important points to consider when using this function: - **Immutability of Input**: The primary feature of this function is that it is non-mutating. The original list passed as the `items` parameter will not be altered. - **Random Module Dependency**: This function relies on the `random.shuffle()` method, which is part of Python's standard `random` module. You must ensure that the `random` module is imported into your script before calling this function. - **Shallow Copy**: The function creat...</t>
         </is>
       </c>
     </row>

--- a/random_module_one.xlsx
+++ b/random_module_one.xlsx
@@ -461,16 +461,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,26 +524,10 @@
           <t>num(a, b)</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>The `num` function calculates and returns the sum of two provided numbers.</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Description | The first number to be used in the addition. | The second number to be used in the addition. |</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>This function performs a basic arithmetic addition. It accepts two arguments, `a` and `b`, and computes their sum using the `+` operator. The resulting value is then returned by the function. The function is straightforward and does not contain any complex logic or error handling. For example, if `a` is `5` and `b` is `10`, the function will compute `5 + 10` and return `15`.</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Important points to consider when using this function: - The function is designed for numeric types like integers (`int`) and floating-point numbers (`float`). - If strings are passed as arguments, the function will perform string concatenation instead of arithmetic addition (e.g., `num("hello", "world")` would return `"helloworld"`). - The order of the parameters `a` and `b` does not affect the result due to the commutative property of addition. **Output Example**: A single numeric value rep...</t>
-        </is>
-      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="4" t="n">
@@ -559,26 +543,10 @@
           <t>generate_random_integers</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>The `generate_random_integers` function creates and returns a list of a specified number of pseudo-random integers within a given inclusive range.</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Description | The total number of random integers to generate. This value must be non-negative. | The inclusive lower bound of the random number range. Defaults to `0`. | The inclusive upper bound of the random number range. Defaults to `100`. |</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>This function provides a straightforward way to generate a list of random integers. The logic proceeds as follows: 1. **Input Validation**: The function first checks if the `count` parameter is a non-negative number. If `count` is less than zero, it raises a `ValueError` because it's impossible to generate a negative number of integers. 2. **Range Correction**: It then compares the `start` and `end` parameters. If `start` is found to be greater than `end`, the function automatically swaps the...</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>- This function depends on Python's `random` module. Ensure it is imported before calling the function. - The function gracefully handles cases where `start &gt; end` by swapping the values internally, so the order of these two parameters does not affect the outcome. - An attempt to generate a negative number of integers (e.g., `count=-1`) will result in a `ValueError`. - The range defined by `start` and `end` is inclusive, meaning both `start` and `end` are potential values in the output list. ...</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -594,22 +562,10 @@
           <t>choose_random_item</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>The `choose_random_item` function selects and returns a single item chosen uniformly at random from a provided list of strings.</t>
-        </is>
-      </c>
+      <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to select a random element from a list. It begins by performing a validation check on the input list `items`. If the list is empty (`if not items`), the function immediately raises a `ValueError` to prevent errors that would occur from attempting to choose an item from an empty sequence. If the list is not empty, the function proceeds to use `random.choice(items)`. This is a standard library function from Python's `random` module that takes a non-empty sequen...</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>* The function requires the `random` module to be imported to work correctly. * Passing an empty list to this function will result in a `ValueError`. Ensure the list contains at least one element before calling. * The function is designed for a `List[str]`, but `random.choice` can work with any non-empty sequence (like tuples or other list types). **Output Example**: A single string from the input list.</t>
-        </is>
-      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -625,26 +581,10 @@
           <t>shuffle_copy</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function returns a new, randomly shuffled copy of a given list without modifying the original list.</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>- `items` (`List[int]`): The list of integers to be shuffled.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to shuffle a list by ensuring the original data structure remains unchanged. The process is straightforward: 1. A shallow copy of the input `items` list is created using `copy = list(items)`. This is the key step that prevents mutation of the original list. 2. The `random.shuffle()` function is then called on this new `copy`. This function shuffles the elements of the list in-place, rearranging them into a random order. 3. Finally, the shuffled `copy` is retu...</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>- **Non-mutating:** The primary benefit of this function is that it does not alter the original list provided as an argument. This prevents unintended side effects in your code. - **Dependency:** This function relies on Python's built-in `random` module. You must ensure `import random` is present in your script for the function to work. - **Type Flexibility:** While the type hint specifies `List[int]`, the function's logic will work correctly with lists containing other data types, such as st...</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -660,96 +600,10 @@
           <t>fibonacci</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>The `fibonacci` function computes the nth number in the Fibonacci sequence using an iterative method.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>- `n` (int): The 0-indexed position in the Fibonacci sequence for which to find the value.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>This function provides an efficient, iterative way to calculate a Fibonacci number. The function begins by validating the input `n`. If `n` is a negative number, it raises a `ValueError` because the Fibonacci sequence is not defined for negative indices. It then initializes two variables, `a` and `b`, to `0` and `1` respectively. These represent the first two numbers in the sequence, F₀ and F₁. The core logic resides in a `for` loop that iterates `n` times. In each iteration, the values of `a...</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>- The input `n` must be a non-negative integer. Providing a negative integer will result in a `ValueError`. - This function uses an iterative approach, which is memory-efficient and avoids the recursion depth limits that can affect recursive solutions for large values of `n`. - The sequence is 0-indexed, meaning `fibonacci(0)` returns the first number (0), `fibonacci(1)` returns the second (1), and so on. **Output Example**:</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>choose_random_item</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>The `choose_random_item` function selects and returns a single, random element from a provided list of strings.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>- `items` (`List[str]`): A list of strings from which a random item will be selected. This list must not be empty.</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>This function provides a straightforward way to get a random element from a sequence. The logic proceeds in two steps: First, it performs a validation check on the input `items` list. The condition `if not items:` evaluates to `True` if the list is empty. In this case, the function raises a `ValueError` to prevent errors in the random selection logic and to enforce the requirement that the input sequence must be non-empty. If the `items` list is not empty, the function uses `random.choice(ite...</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>- The input list `items` cannot be empty. Passing an empty list will result in a `ValueError`. - The function relies on Python's built-in `random` module. Ensure this module is imported and available in the execution environment. - The selection is uniformly random, meaning every string in the `items` list has an equal probability of being returned. **Output Example**: A single string that was present in the input `items` list. For example, `"apple"`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>shuffle_copy</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>The `shuffle_copy` function creates and returns a new list containing the elements of the input list in a randomized order, leaving the original list unchanged.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>- **`items`** (`List[int]`): A list of integers to be copied and shuffled.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a safe way to shuffle a list without altering the original data structure. The logic proceeds in three steps: 1. First, a shallow copy of the input `items` list is created using the `list()` constructor. This ensures that any subsequent modifications do not affect the original list provided by the user. 2. Next, the `random.shuffle()` function is called on the newly created `copy`. The `random.shuffle()` method shuffles the elements of a list "in-place," meaning it dire...</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Important points to consider when using this function: - **Immutability of Input**: The primary feature of this function is that it is non-mutating. The original list passed as the `items` parameter will not be altered. - **Random Module Dependency**: This function relies on the `random.shuffle()` method, which is part of Python's standard `random` module. You must ensure that the `random` module is imported into your script before calling this function. - **Shallow Copy**: The function creat...</t>
-        </is>
-      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
